--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,340 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>49100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>33300</v>
+      </c>
+      <c r="F8" s="3">
         <v>73900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>55200</v>
       </c>
-      <c r="F8" s="3">
-        <v>391900</v>
-      </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
+        <v>58300</v>
+      </c>
+      <c r="I8" s="3">
         <v>978200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>3008800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>201800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2184600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>187300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>153800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>56100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>24000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>26200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>10700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>71300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>103300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>37700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>40300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>69800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>126000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>153300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>102400</v>
+      </c>
+      <c r="F9" s="3">
         <v>143900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>102800</v>
       </c>
-      <c r="F9" s="3">
-        <v>823000</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
+        <v>122500</v>
+      </c>
+      <c r="I9" s="3">
         <v>744000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1264100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>78300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>696800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>81900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>92900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>29000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>4100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>26500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>19900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>10300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>175000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>80700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>36000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>7100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>38600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>62700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>174600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>40600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-69100</v>
+      </c>
+      <c r="F10" s="3">
         <v>-70000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-47600</v>
       </c>
-      <c r="F10" s="3">
-        <v>-431100</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
+        <v>-64200</v>
+      </c>
+      <c r="I10" s="3">
         <v>234200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>1744700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>123500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1487800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>105400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>60800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>27000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>-2500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>6400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>-103700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>22500</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="U10" s="3">
-        <v>100</v>
       </c>
       <c r="V10" s="3">
         <v>1700</v>
       </c>
       <c r="W10" s="3">
+        <v>100</v>
+      </c>
+      <c r="X10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y10" s="3">
         <v>7100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-48500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>112800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,82 +1041,90 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E12" s="3">
+        <v>17200</v>
+      </c>
+      <c r="F12" s="3">
         <v>17900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>19100</v>
       </c>
-      <c r="F12" s="3">
-        <v>223500</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
+        <v>33400</v>
+      </c>
+      <c r="I12" s="3">
         <v>118100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>205100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>15200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>117900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>13200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>9900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>8100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>5600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>4700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>3800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>6500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>9600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>5700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>5600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>4800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>7400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>9800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>5500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>4700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1164,49 +1197,55 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F14" s="3">
         <v>2400</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>51300</v>
+      </c>
+      <c r="I14" s="3">
         <v>11300</v>
       </c>
-      <c r="G14" s="3">
-        <v>11300</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>30400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1238,8 +1277,14 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1264,11 +1309,11 @@
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>16</v>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>16</v>
@@ -1285,35 +1330,41 @@
       <c r="Q15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T15" s="3">
         <v>500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>400</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X15" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0</v>
+      <c r="X15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1388,170 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3">
+        <v>146200</v>
+      </c>
+      <c r="F17" s="3">
         <v>193000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>140900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1227700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1030300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1816100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>116300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>971300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>121400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>130200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>58000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>15200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>37700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>29000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>21800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>194700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>91900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>79600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>16100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>51200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>79700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>188800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>51000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-112900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-119100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-85700</v>
       </c>
-      <c r="F18" s="3">
-        <v>-835800</v>
-      </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>-1169400</v>
+      </c>
+      <c r="I18" s="3">
         <v>-52100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>1192700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>85500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1213300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>65900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>23500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-9900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-13700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-11100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-123400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>11300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-42000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-8900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-10800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-9900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-62800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>102400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1513,82 +1578,90 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
-        <v>48300</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>1051400</v>
+      </c>
+      <c r="I20" s="3">
         <v>110200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>147200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>123400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>7000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>2100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>3600</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="U20" s="3">
-        <v>500</v>
       </c>
       <c r="V20" s="3">
         <v>1500</v>
       </c>
       <c r="W20" s="3">
+        <v>500</v>
+      </c>
+      <c r="X20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y20" s="3">
         <v>1800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>9800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1637,32 +1710,38 @@
       <c r="R21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U21" s="3">
         <v>16500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-39400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3">
         <v>-7000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-52400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1672,8 +1751,8 @@
       <c r="E22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>16</v>
@@ -1681,17 +1760,17 @@
       <c r="H22" s="3">
         <v>0</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1700,147 +1779,159 @@
         <v>0</v>
       </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>100</v>
-      </c>
-      <c r="P22" s="3">
-        <v>200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>200</v>
       </c>
       <c r="R22" s="3">
         <v>200</v>
       </c>
       <c r="S22" s="3">
+        <v>200</v>
+      </c>
+      <c r="T22" s="3">
+        <v>200</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>2000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>2700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>2400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>2400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>100</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-162100</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-100500</v>
+      </c>
+      <c r="F23" s="3">
         <v>-116100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-86700</v>
       </c>
-      <c r="F23" s="3">
-        <v>-787500</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
+        <v>-118000</v>
+      </c>
+      <c r="I23" s="3">
         <v>58000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>1339800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>86000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>1336600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>72800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>24000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-10000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-6300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-122900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>14600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-41000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-10400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-12100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-10600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-55400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>106600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-20400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-2300</v>
       </c>
-      <c r="F24" s="3">
-        <v>-177300</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="I24" s="3">
         <v>-3000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>304400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>20900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>49800</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1869,22 +1960,28 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>-8100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>6700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>13300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2054,174 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="F26" s="3">
         <v>-110700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-84400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-610200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>61100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>1035500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>65100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1286900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>72800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>23900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-10000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-12700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-122900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>14600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-41000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-10400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-4000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-9700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>93300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="F27" s="3">
         <v>-110700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-84400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-610200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>61100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>1035500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>65100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1286900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>72800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>23900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-10000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-12700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-122900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>14600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-41000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-10400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-4000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-9700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>93300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2294,14 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2374,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2454,14 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2534,174 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-48300</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-1051400</v>
+      </c>
+      <c r="I32" s="3">
         <v>-110200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-147200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-123400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-7000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-2100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-500</v>
       </c>
       <c r="V32" s="3">
         <v>-1500</v>
       </c>
       <c r="W32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="X32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-1800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="F33" s="3">
         <v>-110700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-84400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-610200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>61100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>1035500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>65100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1286900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>72800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>23900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-10000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-12700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-122900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>14600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-41000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-10400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-4000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-9700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>93300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2774,179 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="F35" s="3">
         <v>-110700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-84400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-610200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>61100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>1035500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>65100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1286900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>72800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>23900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-10000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-12700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-122900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>14600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-41000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-10400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-4000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-9700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>93300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2973,10 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,68 +3003,70 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>40600</v>
+      </c>
+      <c r="F41" s="3">
         <v>66100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>72000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>101600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2002700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>2640700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2643200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2684300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>241400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>173500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>186200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>54500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>26100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>23100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>41400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>80400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>51200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>42200</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>16</v>
       </c>
@@ -2906,8 +3079,14 @@
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2939,35 +3118,35 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>1200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>8700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>30100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>51200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>27100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>1700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>12500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>17200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W42" s="3" t="s">
         <v>16</v>
       </c>
@@ -2980,68 +3159,74 @@
       <c r="Z42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F43" s="3">
         <v>10100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="3">
         <v>504300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>357900</v>
       </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
       <c r="J43" s="3">
+        <v>0</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
         <v>275000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>14000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>24800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>23700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>26400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3054,68 +3239,74 @@
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>217100</v>
+      </c>
+      <c r="F44" s="3">
         <v>272100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>310500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1685600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1328900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1626200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1193300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>812400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>118400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>83500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>52400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>31400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>7900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>13000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>35500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>30200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>60400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>65500</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3128,68 +3319,74 @@
       <c r="Z44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>122200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>81700</v>
+      </c>
+      <c r="F45" s="3">
         <v>83400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>138300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1427300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1335300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1420300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1937600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1501800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>186200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>201800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>82800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>31700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>37000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>26600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>40800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>74700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>64800</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3202,68 +3399,74 @@
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>363700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>349200</v>
+      </c>
+      <c r="F46" s="3">
         <v>431800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>520800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>555700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>5024700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5687200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5774100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5273500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>546200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>458800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>323500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>140200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>101100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>115400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>145900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>144900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>222500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>216100</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3276,8 +3479,14 @@
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3285,16 +3494,16 @@
         <v>2800</v>
       </c>
       <c r="E47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G47" s="3">
         <v>2900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>20000</v>
       </c>
       <c r="I47" s="3">
         <v>20000</v>
@@ -3303,26 +3512,26 @@
         <v>20000</v>
       </c>
       <c r="K47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="M47" s="3">
         <v>2800</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>400</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3335,11 +3544,11 @@
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
-      </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
@@ -3350,68 +3559,74 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>36300</v>
+      </c>
+      <c r="F48" s="3">
         <v>53400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>72400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>717200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>355400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>357200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>340600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>216500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>7000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>21200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>8200</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3424,49 +3639,55 @@
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>30500</v>
+      </c>
+      <c r="F49" s="3">
         <v>28800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>13400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>12500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>74100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>51300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>45300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>20300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>900</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O49" s="3">
-        <v>0</v>
-      </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="O49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -3498,8 +3719,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3799,14 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,68 +3879,74 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>45400</v>
+      </c>
+      <c r="F52" s="3">
         <v>21700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>24200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>24200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>107300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>78900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>70600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>102000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>500</v>
       </c>
       <c r="M52" s="3">
         <v>400</v>
       </c>
       <c r="N52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
       </c>
       <c r="P52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3">
         <v>300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3720,8 +3959,14 @@
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,68 +4039,74 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>493300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>464100</v>
+      </c>
+      <c r="F54" s="3">
         <v>538400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>633700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>685000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>5581400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>6194700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>6250500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>5632300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>558400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>465900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>328700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>144300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>106800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>133900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>152500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>152700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>245800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>225300</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>16</v>
       </c>
@@ -3868,8 +4119,14 @@
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4153,10 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,68 +4183,70 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F57" s="3">
         <v>27300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>26900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>16700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>32700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>97000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>101200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>143400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>17100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>15300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>10300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>15300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>11500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>9700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>16</v>
       </c>
@@ -3998,8 +4259,14 @@
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4031,35 +4298,35 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>4500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>6800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>7200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>28900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>29700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>19600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>38300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>30800</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4072,68 +4339,74 @@
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>71700</v>
+      </c>
+      <c r="F59" s="3">
         <v>82800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>56000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>395300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>658600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1379100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2093600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1941700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>188600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>176100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>236300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>70500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>15800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>5700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>9100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>53200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>54400</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4146,68 +4419,74 @@
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>90900</v>
+      </c>
+      <c r="F60" s="3">
         <v>110100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>83000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>75300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>691300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1476100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2194800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2085100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>205700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>191400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>247100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>82500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>24500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>36300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>45700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>43900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>103000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>94900</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4220,8 +4499,14 @@
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4294,68 +4579,74 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9800</v>
+      </c>
+      <c r="F62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>2000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>18700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>16900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>85100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>88500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>10500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>3300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2900</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4368,8 +4659,14 @@
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4739,14 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4819,14 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,68 +4899,74 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>145100</v>
+      </c>
+      <c r="E66" s="3">
+        <v>100700</v>
+      </c>
+      <c r="F66" s="3">
         <v>112300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>85600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>77300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>710000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1492900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2280000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2173600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>208300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>201900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>248300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>84100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>26700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>38900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>49000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>46000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>105700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>97800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4664,8 +4979,14 @@
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +5013,10 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +5089,14 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5169,14 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5249,14 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,68 +5329,74 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-204600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-65700</v>
+      </c>
+      <c r="F72" s="3">
         <v>14400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>125100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>209400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1932800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1886700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1277800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>900800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-65800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-121100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-152700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-152900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-151300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-138500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-144500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-136000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-13100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-28000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5062,8 +5409,14 @@
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5489,14 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5569,14 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,68 +5649,74 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>348200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>363400</v>
+      </c>
+      <c r="F76" s="3">
         <v>426100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>548100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>607700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4871400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4701800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3970600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3458700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>350100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>264000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>80500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>60200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>80100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>95000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>103500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>106700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>140100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>127500</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5358,8 +5729,14 @@
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5809,179 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-80100</v>
+      </c>
+      <c r="F81" s="3">
         <v>-110700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-84400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-610200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>61100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>1035500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>65100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1286900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>72800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>23900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-10000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-12700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-122900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>14600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-41000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-10400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-4000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-9700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-62200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>93300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +6008,10 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5666,11 +6063,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>16</v>
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>16</v>
@@ -5687,8 +6084,14 @@
       <c r="Z83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +6164,14 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6244,14 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6324,14 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6404,14 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,8 +6484,14 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6071,15 +6504,15 @@
       <c r="F89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G89" s="3">
+      <c r="G89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" s="3">
         <v>-582200</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6089,11 +6522,11 @@
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O89" s="3">
         <v>0</v>
@@ -6110,11 +6543,11 @@
       <c r="S89" s="3">
         <v>0</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>16</v>
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>16</v>
@@ -6131,8 +6564,14 @@
       <c r="Z89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,8 +6598,10 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6212,11 +6653,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>16</v>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>16</v>
@@ -6233,8 +6674,14 @@
       <c r="Z91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6754,14 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,8 +6834,14 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6395,15 +6854,15 @@
       <c r="F94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G94" s="3">
+      <c r="G94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" s="3">
         <v>-40300</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6413,11 +6872,11 @@
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O94" s="3">
         <v>0</v>
@@ -6434,11 +6893,11 @@
       <c r="S94" s="3">
         <v>0</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>16</v>
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>16</v>
@@ -6455,8 +6914,14 @@
       <c r="Z94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6948,10 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6557,8 +7024,14 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +7104,14 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +7184,14 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,8 +7264,14 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6793,15 +7284,15 @@
       <c r="F100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G100" s="3">
+      <c r="G100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" s="3">
         <v>-315600</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
@@ -6811,11 +7302,11 @@
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O100" s="3">
         <v>0</v>
@@ -6832,11 +7323,11 @@
       <c r="S100" s="3">
         <v>0</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>16</v>
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
       </c>
       <c r="V100" s="3" t="s">
         <v>16</v>
@@ -6853,8 +7344,14 @@
       <c r="Z100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6867,15 +7364,15 @@
       <c r="F101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3">
         <v>209000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
@@ -6885,11 +7382,11 @@
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6906,11 +7403,11 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>16</v>
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3" t="s">
         <v>16</v>
@@ -6927,8 +7424,14 @@
       <c r="Z101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6941,15 +7444,15 @@
       <c r="F102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G102" s="3">
+      <c r="G102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="3">
         <v>-729000</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>16</v>
       </c>
@@ -6959,11 +7462,11 @@
       <c r="L102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
-      <c r="N102" s="3">
-        <v>0</v>
+      <c r="M102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O102" s="3">
         <v>0</v>
@@ -6980,11 +7483,11 @@
       <c r="S102" s="3">
         <v>0</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>16</v>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>16</v>
@@ -6999,6 +7502,12 @@
         <v>16</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E8" s="3">
         <v>49100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>33300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>73900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>55200</v>
       </c>
-      <c r="H8" s="3">
-        <v>58300</v>
-      </c>
       <c r="I8" s="3">
+        <v>47400</v>
+      </c>
+      <c r="J8" s="3">
         <v>978200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3008800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>201800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2184600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>153800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>56100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>24000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>26200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>71300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>103300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>37700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>69800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>126000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>153300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E9" s="3">
         <v>103100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>102400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>143900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>102800</v>
       </c>
-      <c r="H9" s="3">
-        <v>122500</v>
-      </c>
       <c r="I9" s="3">
+        <v>939900</v>
+      </c>
+      <c r="J9" s="3">
         <v>744000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1264100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>78300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>696800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>81900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>92900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>29000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>4100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>175000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>80700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>36000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>38600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>62700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>174600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>40600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="E10" s="3">
         <v>-54000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-69100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-70000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-47600</v>
       </c>
-      <c r="H10" s="3">
-        <v>-64200</v>
-      </c>
       <c r="I10" s="3">
+        <v>-892500</v>
+      </c>
+      <c r="J10" s="3">
         <v>234200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1744700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>123500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1487800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>105400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>60800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>27000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-2500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-103700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>7100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>112800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,88 +1056,92 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E12" s="3">
         <v>10800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>17200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19100</v>
       </c>
-      <c r="H12" s="3">
-        <v>33400</v>
-      </c>
       <c r="I12" s="3">
+        <v>32800</v>
+      </c>
+      <c r="J12" s="3">
         <v>118100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>205100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>15200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>117900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>13200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>9900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>8100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3800</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>6500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>9600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5700</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>4800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>7400</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>4700</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1203,43 +1220,46 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-6200</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F14" s="3">
         <v>2200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2400</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
-        <v>51300</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>67200</v>
+      </c>
+      <c r="J14" s="3">
         <v>11300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>16</v>
@@ -1247,8 +1267,8 @@
       <c r="P14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1283,8 +1303,11 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1315,8 +1338,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>16</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>16</v>
@@ -1336,15 +1359,15 @@
       <c r="S15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U15" s="3">
         <v>500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>400</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1354,8 +1377,8 @@
       <c r="Y15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z15" s="3">
-        <v>0</v>
+      <c r="Z15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1363,8 +1386,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>16</v>
+      <c r="D17" s="3">
+        <v>103100</v>
       </c>
       <c r="E17" s="3">
+        <v>142300</v>
+      </c>
+      <c r="F17" s="3">
         <v>146200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>193000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>140900</v>
       </c>
-      <c r="H17" s="3">
-        <v>1227700</v>
-      </c>
       <c r="I17" s="3">
+        <v>183600</v>
+      </c>
+      <c r="J17" s="3">
         <v>1030300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1816100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>116300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>971300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>121400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>130200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>58000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>29000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>194700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>91900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>79600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>16100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>51200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>79700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>188800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>51000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>16</v>
+      <c r="D18" s="3">
+        <v>-68000</v>
       </c>
       <c r="E18" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-112900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-119100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-85700</v>
       </c>
-      <c r="H18" s="3">
-        <v>-1169400</v>
-      </c>
       <c r="I18" s="3">
+        <v>-136200</v>
+      </c>
+      <c r="J18" s="3">
         <v>-52100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1192700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>85500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1213300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>65900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-11100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-123400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>11300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-42000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-8900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>102400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1580,88 +1613,92 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>16</v>
+      <c r="D20" s="3">
+        <v>29400</v>
       </c>
       <c r="E20" s="3">
+        <v>-68900</v>
+      </c>
+      <c r="F20" s="3">
         <v>12300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3">
-        <v>1051400</v>
-      </c>
       <c r="I20" s="3">
+        <v>12700</v>
+      </c>
+      <c r="J20" s="3">
         <v>110200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>147200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>123400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>9800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1716,32 +1753,35 @@
       <c r="T21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="3">
         <v>16500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-39400</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1757,23 +1797,23 @@
       <c r="G22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1785,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>100</v>
-      </c>
-      <c r="R22" s="3">
-        <v>200</v>
       </c>
       <c r="S22" s="3">
         <v>200</v>
@@ -1797,144 +1837,150 @@
         <v>200</v>
       </c>
       <c r="U22" s="3">
+        <v>200</v>
+      </c>
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>2400</v>
       </c>
       <c r="Z22" s="3">
         <v>2400</v>
       </c>
       <c r="AA22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-38600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-162100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-100500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-116100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-86700</v>
       </c>
-      <c r="H23" s="3">
-        <v>-118000</v>
-      </c>
       <c r="I23" s="3">
+        <v>-123500</v>
+      </c>
+      <c r="J23" s="3">
         <v>58000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1339800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>86000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1336600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>72800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-122900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>14600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-41000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>106600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-23100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-20400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-2300</v>
       </c>
-      <c r="H24" s="3">
-        <v>-26400</v>
-      </c>
       <c r="I24" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="J24" s="3">
         <v>-3000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>304400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>20900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>49800</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1966,22 +2012,25 @@
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-8100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>6700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>13300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>16</v>
+      <c r="D26" s="3">
+        <v>-39400</v>
       </c>
       <c r="E26" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-80100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-110700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-84400</v>
       </c>
-      <c r="H26" s="3">
-        <v>-610200</v>
-      </c>
       <c r="I26" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="J26" s="3">
         <v>61100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1035500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>65100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1286900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>72800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-12700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-122900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-41000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>93300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>16</v>
+      <c r="D27" s="3">
+        <v>-39400</v>
       </c>
       <c r="E27" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-80100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-110700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-84400</v>
       </c>
-      <c r="H27" s="3">
-        <v>-610200</v>
-      </c>
       <c r="I27" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="J27" s="3">
         <v>61100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1035500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>65100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1286900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>72800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-12700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-122900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-41000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>93300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2380,8 +2441,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>16</v>
+      <c r="D32" s="3">
+        <v>-29400</v>
       </c>
       <c r="E32" s="3">
+        <v>68900</v>
+      </c>
+      <c r="F32" s="3">
         <v>-12300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3">
-        <v>-1051400</v>
-      </c>
       <c r="I32" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="J32" s="3">
         <v>-110200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-147200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-123400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>16</v>
+      <c r="D33" s="3">
+        <v>-39400</v>
       </c>
       <c r="E33" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-80100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-110700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-84400</v>
       </c>
-      <c r="H33" s="3">
-        <v>-610200</v>
-      </c>
       <c r="I33" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="J33" s="3">
         <v>61100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1035500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>65100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1286900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>72800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-12700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-122900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-41000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>93300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>16</v>
+      <c r="D35" s="3">
+        <v>-39400</v>
       </c>
       <c r="E35" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-80100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-110700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-84400</v>
       </c>
-      <c r="H35" s="3">
-        <v>-610200</v>
-      </c>
       <c r="I35" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="J35" s="3">
         <v>61100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1035500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>65100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1286900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>72800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-12700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-122900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-41000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>93300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,71 +3091,72 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E41" s="3">
         <v>96200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>40600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>66100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>101600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2002700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2640700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2643200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2684300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>241400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>173500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>186200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>54500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>23100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>80400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>51200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>42200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3085,8 +3172,11 @@
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3124,32 +3214,32 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>1200</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>30100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>51200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>12500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>17200</v>
       </c>
-      <c r="W42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3165,71 +3255,74 @@
       <c r="AB42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E43" s="3">
         <v>3000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10100</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="3">
         <v>504300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>357900</v>
       </c>
-      <c r="J43" s="3">
-        <v>0</v>
-      </c>
       <c r="K43" s="3">
         <v>0</v>
       </c>
       <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
         <v>275000</v>
-      </c>
-      <c r="M43" s="3">
-        <v>100</v>
       </c>
       <c r="N43" s="3">
         <v>100</v>
       </c>
       <c r="O43" s="3">
+        <v>100</v>
+      </c>
+      <c r="P43" s="3">
         <v>1000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>14000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>24800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>23700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>26400</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3245,71 +3338,74 @@
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E44" s="3">
         <v>142300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>217100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>272100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>310500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1685600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1328900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1626200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1193300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>812400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>118400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>83500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>52400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>31400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>35500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>30200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>60400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>65500</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3325,71 +3421,74 @@
       <c r="AB44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>165400</v>
+      </c>
+      <c r="E45" s="3">
         <v>122200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>81700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>83400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>138300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1427300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1335300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1420300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1937600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1501800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>186200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>201800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>31700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>37000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>40800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>74700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>64800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3405,71 +3504,74 @@
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>321000</v>
+      </c>
+      <c r="E46" s="3">
         <v>363700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>349200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>431800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>520800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>555700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5024700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5687200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5774100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5273500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>546200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>458800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>323500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>140200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>101100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>115400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>145900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>144900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>222500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>216100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3485,8 +3587,11 @@
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3500,13 +3605,13 @@
         <v>2800</v>
       </c>
       <c r="G47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="H47" s="3">
         <v>2900</v>
       </c>
       <c r="I47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="J47" s="3">
         <v>20000</v>
@@ -3518,11 +3623,11 @@
         <v>20000</v>
       </c>
       <c r="M47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="N47" s="3">
         <v>2800</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
@@ -3530,11 +3635,11 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>400</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3550,8 +3655,8 @@
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -3565,71 +3670,74 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>51300</v>
+      </c>
+      <c r="E48" s="3">
         <v>31200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>36300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>53400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>717200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>355400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>357200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>340600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>216500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>18200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8200</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3645,52 +3753,55 @@
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>91200</v>
+      </c>
+      <c r="E49" s="3">
         <v>28300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>12500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>74100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>51300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>45300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>20300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -3725,8 +3836,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,46 +4002,49 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E52" s="3">
         <v>67300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>45400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>24200</v>
       </c>
       <c r="H52" s="3">
         <v>24200</v>
       </c>
       <c r="I52" s="3">
+        <v>24200</v>
+      </c>
+      <c r="J52" s="3">
         <v>107300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>78900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>70600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>102000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
@@ -3933,23 +4053,23 @@
         <v>400</v>
       </c>
       <c r="R52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="S52" s="3">
         <v>300</v>
       </c>
       <c r="T52" s="3">
+        <v>300</v>
+      </c>
+      <c r="U52" s="3">
         <v>800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>16</v>
       </c>
@@ -3965,8 +4085,11 @@
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,71 +4168,74 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>534100</v>
+      </c>
+      <c r="E54" s="3">
         <v>493300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>464100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>538400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>633700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>685000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5581400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6194700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6250500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5632300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>558400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>465900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>328700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>144300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>106800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>133900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>152500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>152700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>245800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>225300</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4125,8 +4251,11 @@
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,71 +4315,72 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E57" s="3">
         <v>6200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>27300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>97000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>143400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>10300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9700</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4265,8 +4396,11 @@
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4304,32 +4438,32 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>4500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>7200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>28900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>29700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>19600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>38300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>30800</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4345,71 +4479,74 @@
       <c r="AB58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>88600</v>
+        <v>93800</v>
       </c>
       <c r="E59" s="3">
+        <v>128900</v>
+      </c>
+      <c r="F59" s="3">
         <v>71700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>56000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>395300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>658600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1379100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2093600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1941700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>188600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>176100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>236300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>70500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>53200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>54400</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4425,71 +4562,74 @@
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>110500</v>
+      </c>
+      <c r="E60" s="3">
         <v>135200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>90900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>83000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>691300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1476100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2194800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2085100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>205700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>191400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>247100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>82500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>36300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>45700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>43900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>103000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>94900</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4505,8 +4645,11 @@
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4585,71 +4728,74 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E62" s="3">
         <v>9900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>16900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>85100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>88500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2900</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4665,8 +4811,11 @@
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,71 +5060,74 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E66" s="3">
         <v>145100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>100700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>112300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>77300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>710000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1492900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2280000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2173600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>208300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>201900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>248300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>84100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>38900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>49000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>46000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>105700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>97800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>16</v>
       </c>
@@ -4985,8 +5143,11 @@
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,71 +5506,74 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-204600</v>
+        <v>-225200</v>
       </c>
       <c r="E72" s="3">
+        <v>-204700</v>
+      </c>
+      <c r="F72" s="3">
         <v>-65700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>14400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>125100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>209400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1932800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1886700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1277800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>900800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-65800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-121100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-152900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-151300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-138500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-144500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-136000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-13100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-28000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5415,8 +5589,11 @@
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,71 +5838,74 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>411700</v>
+      </c>
+      <c r="E76" s="3">
         <v>348200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>363400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>426100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>548100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>607700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4871400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4701800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3970600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3458700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>350100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>264000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>80500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>60200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>95000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>103500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>106700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>140100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>127500</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5735,8 +5921,11 @@
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>16</v>
+      <c r="D81" s="3">
+        <v>-39400</v>
       </c>
       <c r="E81" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-80100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-110700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-84400</v>
       </c>
-      <c r="H81" s="3">
-        <v>-610200</v>
-      </c>
       <c r="I81" s="3">
+        <v>-96300</v>
+      </c>
+      <c r="J81" s="3">
         <v>61100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1035500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>65100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1286900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>72800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-12700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-122900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-41000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>93300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,8 +6208,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6069,8 +6268,8 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>16</v>
+      <c r="V83" s="3">
+        <v>0</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>16</v>
@@ -6090,8 +6289,11 @@
       <c r="AB83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,8 +6704,11 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6511,11 +6728,11 @@
         <v>16</v>
       </c>
       <c r="I89" s="3">
+        <v>-182600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-582200</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6528,8 +6745,8 @@
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O89" s="3">
-        <v>0</v>
+      <c r="O89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P89" s="3">
         <v>0</v>
@@ -6549,8 +6766,8 @@
       <c r="U89" s="3">
         <v>0</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>16</v>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>16</v>
@@ -6570,8 +6787,11 @@
       <c r="AB89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,13 +6820,14 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-7800</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -6659,8 +6880,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>16</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>16</v>
@@ -6680,8 +6901,11 @@
       <c r="AB91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,8 +7067,11 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6861,11 +7091,11 @@
         <v>16</v>
       </c>
       <c r="I94" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-40300</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K94" s="3" t="s">
         <v>16</v>
       </c>
@@ -6878,8 +7108,8 @@
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P94" s="3">
         <v>0</v>
@@ -6899,8 +7129,8 @@
       <c r="U94" s="3">
         <v>0</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>16</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>16</v>
@@ -6920,8 +7150,11 @@
       <c r="AB94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,8 +7183,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7030,8 +7264,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7513,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7291,11 +7537,11 @@
         <v>16</v>
       </c>
       <c r="I100" s="3">
+        <v>-56200</v>
+      </c>
+      <c r="J100" s="3">
         <v>-315600</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7308,8 +7554,8 @@
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
+      <c r="O100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P100" s="3">
         <v>0</v>
@@ -7329,8 +7575,8 @@
       <c r="U100" s="3">
         <v>0</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>16</v>
+      <c r="V100" s="3">
+        <v>0</v>
       </c>
       <c r="W100" s="3" t="s">
         <v>16</v>
@@ -7350,8 +7596,11 @@
       <c r="AB100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7371,11 +7620,11 @@
         <v>16</v>
       </c>
       <c r="I101" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="J101" s="3">
         <v>209000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7388,8 +7637,8 @@
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7409,8 +7658,8 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>16</v>
+      <c r="V101" s="3">
+        <v>0</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>16</v>
@@ -7430,8 +7679,11 @@
       <c r="AB101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7451,11 +7703,11 @@
         <v>16</v>
       </c>
       <c r="I102" s="3">
+        <v>-326900</v>
+      </c>
+      <c r="J102" s="3">
         <v>-729000</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7468,8 +7720,8 @@
       <c r="N102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
+      <c r="O102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P102" s="3">
         <v>0</v>
@@ -7489,8 +7741,8 @@
       <c r="U102" s="3">
         <v>0</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>16</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>16</v>
@@ -7508,6 +7760,9 @@
         <v>16</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,378 +656,391 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>71900</v>
+      </c>
+      <c r="E8" s="3">
         <v>35100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>49100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>33300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>55200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>47400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>978200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3008800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>201800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2184600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>153800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>24000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>71300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>103300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>37700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>40300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>69800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>126000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>153300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E9" s="3">
         <v>72400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>103100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>102400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>143900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>102800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>939900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>744000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1264100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>78300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>696800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>81900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>92900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>29000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>10300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>175000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>80700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>36000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>7100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>62700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>174600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>40600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E10" s="3">
         <v>-37300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-54000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-69100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-70000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-47600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-892500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>234200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1744700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>123500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1487800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>105400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>60800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>27000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-2500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-103700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>7100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>112800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,91 +1070,95 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E12" s="3">
         <v>15300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>10800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>17200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>17900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>118100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>205100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>15200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>117900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>13200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>9900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>8100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>4700</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>6500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>9800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5500</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,46 +1240,49 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>21300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>67200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>30400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
+      <c r="N14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>16</v>
@@ -1270,8 +1290,8 @@
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1306,8 +1326,11 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1341,8 +1364,8 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>16</v>
+      <c r="N15" s="3">
+        <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
         <v>16</v>
@@ -1362,15 +1385,15 @@
       <c r="T15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="V15" s="3">
         <v>500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>400</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1380,8 +1403,8 @@
       <c r="Z15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1389,8 +1412,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1443,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>118500</v>
+      </c>
+      <c r="E17" s="3">
         <v>103100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>142300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>146200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>193000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>140900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>183600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1030300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1816100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>116300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>971300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>121400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>130200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>58000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>15200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>29000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>194700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>91900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>79600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>16100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>51200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>79700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>188800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>51000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-46600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-68000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-93200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-112900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-119100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-85700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-136200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-52100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1192700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>85500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1213300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>65900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-9900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-11100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-123400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-42000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>102400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1614,91 +1647,95 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E20" s="3">
         <v>29400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-68900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>12300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>110200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>147200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>123400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>7000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -1756,37 +1793,40 @@
       <c r="U21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W21" s="3">
         <v>16500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-39400</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>16</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>16</v>
@@ -1800,23 +1840,23 @@
       <c r="H22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1828,10 +1868,10 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>100</v>
-      </c>
-      <c r="S22" s="3">
-        <v>200</v>
       </c>
       <c r="T22" s="3">
         <v>200</v>
@@ -1840,150 +1880,156 @@
         <v>200</v>
       </c>
       <c r="V22" s="3">
+        <v>200</v>
+      </c>
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>2000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>2400</v>
       </c>
       <c r="AA22" s="3">
         <v>2400</v>
       </c>
       <c r="AB22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-38600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-162100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-116100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-86700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-123500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1339800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>86000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1336600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>72800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>24000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-12700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-122900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>14600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-41000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-12100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>106600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-23100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-20400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-27200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>304400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>20900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>49800</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -2015,22 +2061,25 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-8100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>6700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>13300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2161,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-39400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-139000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-80100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-110700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-84400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-96300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>61100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1035500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>65100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1286900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>72800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-10000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-12700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-122900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>14600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-41000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>93300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-139000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-80100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-110700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-84400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-96300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>61100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1035500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>65100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1286900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>72800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-10000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-12700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-122900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-41000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>93300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2419,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2444,8 +2505,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2591,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2677,183 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-29400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>68900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-12300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-110200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-147200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-123400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-7000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-139000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-80100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-110700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-84400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-96300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>61100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1035500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>65100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1286900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>72800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>23900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-10000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-12700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-122900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-41000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>93300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2935,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-139000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-80100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-110700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-84400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-96300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>61100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1035500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>65100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1286900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>72800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>23900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-10000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-12700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-122900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-41000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>93300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3146,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,74 +3178,75 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E41" s="3">
         <v>54700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>96200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>40600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>101600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2002700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2640700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2643200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2684300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>241400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>173500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>186200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>54500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>26100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>41400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>80400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42200</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3175,8 +3262,11 @@
       <c r="AC41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3217,32 +3307,32 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>1200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>8700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>30100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>51200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>27100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>12500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>17200</v>
       </c>
-      <c r="X42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3258,74 +3348,77 @@
       <c r="AC42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10100</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="3">
         <v>504300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>357900</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
       <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3">
         <v>275000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>100</v>
       </c>
       <c r="O43" s="3">
         <v>100</v>
       </c>
       <c r="P43" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>14000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>24800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>23700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>26400</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3341,74 +3434,77 @@
       <c r="AC43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E44" s="3">
         <v>99200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>142300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>217100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>272100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>310500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1685600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1328900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1626200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1193300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>812400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>118400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>83500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>52400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>31400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>35500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>30200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>60400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>65500</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3424,74 +3520,77 @@
       <c r="AC44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E45" s="3">
         <v>165400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>122200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>81700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>83400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>138300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1427300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1335300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1420300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1937600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1501800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>186200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>201800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>82800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>31700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>37000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>40800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>74700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>64800</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3507,74 +3606,77 @@
       <c r="AC45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>336000</v>
+      </c>
+      <c r="E46" s="3">
         <v>321000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>363700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>349200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>431800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>520800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>555700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5024700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5687200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5774100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5273500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>546200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>458800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>323500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>101100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>115400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>145900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>144900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>222500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>216100</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3590,8 +3692,11 @@
       <c r="AC46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3608,13 +3713,13 @@
         <v>2800</v>
       </c>
       <c r="H47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="I47" s="3">
         <v>2900</v>
       </c>
       <c r="J47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="K47" s="3">
         <v>20000</v>
@@ -3626,11 +3731,11 @@
         <v>20000</v>
       </c>
       <c r="N47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="O47" s="3">
         <v>2800</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -3638,11 +3743,11 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>400</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3658,8 +3763,8 @@
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -3673,74 +3778,77 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E48" s="3">
         <v>51300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>36300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>53400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>717200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>355400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>357200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>340600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>216500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>18200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8200</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3756,55 +3864,58 @@
       <c r="AC48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E49" s="3">
         <v>91200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>12500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>74100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>51300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>45300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>20300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -3839,8 +3950,11 @@
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4036,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,49 +4122,52 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>69900</v>
+      </c>
+      <c r="E52" s="3">
         <v>67800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>67300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>45400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21700</v>
-      </c>
-      <c r="H52" s="3">
-        <v>24200</v>
       </c>
       <c r="I52" s="3">
         <v>24200</v>
       </c>
       <c r="J52" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K52" s="3">
         <v>107300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>78900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>70600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>102000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
       </c>
       <c r="Q52" s="3">
         <v>400</v>
@@ -4056,23 +4176,23 @@
         <v>400</v>
       </c>
       <c r="S52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="T52" s="3">
         <v>300</v>
       </c>
       <c r="U52" s="3">
+        <v>300</v>
+      </c>
+      <c r="V52" s="3">
         <v>800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>2000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4088,8 +4208,11 @@
       <c r="AC52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,74 +4294,77 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>525500</v>
+      </c>
+      <c r="E54" s="3">
         <v>534100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>493300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>464100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>538400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>633700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>685000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5581400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6194700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6250500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5632300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>558400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>465900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>328700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>144300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>106800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>133900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>152500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>152700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>245800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>225300</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4254,8 +4380,11 @@
       <c r="AC54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4414,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,74 +4446,75 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E57" s="3">
         <v>16700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>6200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>19200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>97000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>143400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>10300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>11500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9700</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4399,8 +4530,11 @@
       <c r="AC57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4441,32 +4575,32 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>4500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>7200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>28900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>29700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>19600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>38300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30800</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4482,74 +4616,77 @@
       <c r="AC58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E59" s="3">
         <v>93800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>128900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>71700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>56000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>395300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>658600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1379100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2093600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1941700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>188600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>176100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>236300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>9100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>53200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>54400</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4565,74 +4702,77 @@
       <c r="AC59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>116800</v>
+      </c>
+      <c r="E60" s="3">
         <v>110500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>135200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>110100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>83000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>691300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1476100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2194800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2085100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>205700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>191400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>247100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>82500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>36300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>45700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>43900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>94900</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4648,13 +4788,16 @@
       <c r="AC60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>19200</v>
       </c>
       <c r="E61" s="3">
         <v>0</v>
@@ -4731,74 +4874,77 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E62" s="3">
         <v>11900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>16900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>88500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>10500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2900</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4814,8 +4960,11 @@
       <c r="AC62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5046,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5132,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,74 +5218,77 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E66" s="3">
         <v>122400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>145100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>100700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>112300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>85600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>77300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>710000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1492900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2280000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2173600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>208300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>201900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>248300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>84100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>49000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>46000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>105700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>97800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5146,8 +5304,11 @@
       <c r="AC66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5338,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5422,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5508,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5594,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,74 +5680,77 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-267100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-225200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-204700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-65700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>14400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>125100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>209400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1932800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1886700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1277800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>900800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-65800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-121100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-152700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-152900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-151300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-138500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-144500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-136000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-13100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-28000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5592,8 +5766,11 @@
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5852,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5938,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,74 +6024,77 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>378200</v>
+      </c>
+      <c r="E76" s="3">
         <v>411700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>348200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>363400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>426100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>548100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>607700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4871400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4701800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3970600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3458700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>350100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>264000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>80500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>60200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>80100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>95000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>103500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>106700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>140100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>127500</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>16</v>
       </c>
@@ -5924,8 +6110,11 @@
       <c r="AC76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6196,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-139000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-80100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-110700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-84400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-96300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>61100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1035500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>65100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1286900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>72800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>23900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-10000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-12700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-122900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-41000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>93300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,8 +6407,9 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6271,8 +6470,8 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>16</v>
+      <c r="W83" s="3">
+        <v>0</v>
       </c>
       <c r="X83" s="3" t="s">
         <v>16</v>
@@ -6292,8 +6491,11 @@
       <c r="AC83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6577,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6663,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6749,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6835,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,8 +6921,11 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6727,15 +6944,15 @@
       <c r="H89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J89" s="3">
         <v>-182600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-582200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6748,8 +6965,8 @@
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P89" s="3">
-        <v>0</v>
+      <c r="P89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q89" s="3">
         <v>0</v>
@@ -6769,8 +6986,8 @@
       <c r="V89" s="3">
         <v>0</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>16</v>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>16</v>
@@ -6790,8 +7007,11 @@
       <c r="AC89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,8 +7041,9 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6883,8 +7104,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>16</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>16</v>
@@ -6904,8 +7125,11 @@
       <c r="AC91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7211,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,8 +7297,11 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7090,15 +7320,15 @@
       <c r="H94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J94" s="3">
         <v>-8100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-40300</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7111,8 +7341,8 @@
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
+      <c r="P94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q94" s="3">
         <v>0</v>
@@ -7132,8 +7362,8 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>16</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>16</v>
@@ -7153,8 +7383,11 @@
       <c r="AC94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7417,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7267,8 +7501,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7587,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7673,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,8 +7759,11 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7536,15 +7782,15 @@
       <c r="H100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J100" s="3">
         <v>-56200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-315600</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7557,8 +7803,8 @@
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
+      <c r="P100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q100" s="3">
         <v>0</v>
@@ -7578,8 +7824,8 @@
       <c r="V100" s="3">
         <v>0</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>16</v>
+      <c r="W100" s="3">
+        <v>0</v>
       </c>
       <c r="X100" s="3" t="s">
         <v>16</v>
@@ -7599,8 +7845,11 @@
       <c r="AC100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7619,15 +7868,15 @@
       <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3">
         <v>-80000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>209000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7640,8 +7889,8 @@
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7661,8 +7910,8 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>16</v>
+      <c r="W101" s="3">
+        <v>0</v>
       </c>
       <c r="X101" s="3" t="s">
         <v>16</v>
@@ -7682,8 +7931,11 @@
       <c r="AC101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -7702,15 +7954,15 @@
       <c r="H102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I102" s="3">
+      <c r="I102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J102" s="3">
         <v>-326900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-729000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7723,8 +7975,8 @@
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
+      <c r="P102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Q102" s="3">
         <v>0</v>
@@ -7744,8 +7996,8 @@
       <c r="V102" s="3">
         <v>0</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>16</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>16</v>
@@ -7763,6 +8015,9 @@
         <v>16</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,391 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E8" s="3">
         <v>71900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>35100</v>
       </c>
-      <c r="F8" s="3">
-        <v>49100</v>
-      </c>
       <c r="G8" s="3">
+        <v>104300</v>
+      </c>
+      <c r="H8" s="3">
         <v>33300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>73900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>55200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>47400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>978200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3008800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>201800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2184600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>187300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>153800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>24000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>10700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>71300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>103300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>37700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>40300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>69800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>126000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>153300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E9" s="3">
         <v>91000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>72400</v>
       </c>
-      <c r="F9" s="3">
-        <v>103100</v>
-      </c>
       <c r="G9" s="3">
+        <v>205900</v>
+      </c>
+      <c r="H9" s="3">
         <v>102400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>143900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>102800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>939900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>744000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1264100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>78300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>696800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>81900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>92900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>29000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>175000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>80700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>36000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>7100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>62700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>174600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>40600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-19100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-37300</v>
       </c>
-      <c r="F10" s="3">
-        <v>-54000</v>
-      </c>
       <c r="G10" s="3">
+        <v>-101600</v>
+      </c>
+      <c r="H10" s="3">
         <v>-69100</v>
       </c>
-      <c r="H10" s="3">
-        <v>-70000</v>
-      </c>
       <c r="I10" s="3">
-        <v>-47600</v>
+        <v>-70100</v>
       </c>
       <c r="J10" s="3">
+        <v>-47500</v>
+      </c>
+      <c r="K10" s="3">
         <v>-892500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>234200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1744700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>123500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1487800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>105400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>60800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>27000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-2500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>6400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-103700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>7100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>112800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1071,94 +1084,98 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E12" s="3">
         <v>14600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>15300</v>
       </c>
-      <c r="F12" s="3">
-        <v>10800</v>
-      </c>
       <c r="G12" s="3">
+        <v>29800</v>
+      </c>
+      <c r="H12" s="3">
         <v>17200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>17900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>19100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>32800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>118100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>205100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>15200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>117900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>13200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>9900</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>8100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>4700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>3800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>6500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>9600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5700</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>5600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>4800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>7400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5500</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>4700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1243,49 +1260,52 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E14" s="3">
         <v>800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
-        <v>21300</v>
+        <v>400</v>
       </c>
       <c r="G14" s="3">
-        <v>2200</v>
+        <v>80300</v>
       </c>
       <c r="H14" s="3">
-        <v>2400</v>
+        <v>5700</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
+        <v>9100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="3">
         <v>67200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>30400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>16</v>
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
@@ -1293,8 +1313,8 @@
       <c r="R14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1329,31 +1349,34 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>14900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>8400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>17600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1367,8 +1390,8 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>16</v>
+      <c r="O15" s="3">
+        <v>0</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>16</v>
@@ -1388,15 +1411,15 @@
       <c r="U15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="W15" s="3">
         <v>500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>400</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1406,8 +1429,8 @@
       <c r="AA15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1415,8 +1438,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1444,180 +1470,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>118500</v>
+        <v>124000</v>
       </c>
       <c r="E17" s="3">
+        <v>117700</v>
+      </c>
+      <c r="F17" s="3">
         <v>103100</v>
       </c>
-      <c r="F17" s="3">
-        <v>142300</v>
-      </c>
       <c r="G17" s="3">
-        <v>146200</v>
+        <v>262100</v>
       </c>
       <c r="H17" s="3">
-        <v>193000</v>
+        <v>140500</v>
       </c>
       <c r="I17" s="3">
+        <v>183800</v>
+      </c>
+      <c r="J17" s="3">
         <v>140900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>183600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1030300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1816100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>116300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>971300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>121400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>130200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>58000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>15200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>29000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>194700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>91900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>79600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>16100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>51200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>79700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>188800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>51000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>-46600</v>
+        <v>-50400</v>
       </c>
       <c r="E18" s="3">
+        <v>-45800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-68000</v>
       </c>
-      <c r="F18" s="3">
-        <v>-93200</v>
-      </c>
       <c r="G18" s="3">
-        <v>-112900</v>
+        <v>-157800</v>
       </c>
       <c r="H18" s="3">
-        <v>-119100</v>
+        <v>-107200</v>
       </c>
       <c r="I18" s="3">
+        <v>-110000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-85700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-136200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-52100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1192700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>85500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1213300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>65900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-9900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-13700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-11100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-123400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-42000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>102400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1648,117 +1681,121 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>2800</v>
+        <v>-2900</v>
       </c>
       <c r="E20" s="3">
-        <v>29400</v>
+        <v>-2800</v>
       </c>
       <c r="F20" s="3">
-        <v>-68900</v>
+        <v>-29600</v>
       </c>
       <c r="G20" s="3">
-        <v>12300</v>
+        <v>11400</v>
       </c>
       <c r="H20" s="3">
-        <v>2900</v>
+        <v>-12200</v>
       </c>
       <c r="I20" s="3">
-        <v>-1000</v>
+        <v>-2800</v>
       </c>
       <c r="J20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K20" s="3">
         <v>12700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>110200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>147200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>123400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>7000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>4300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>16</v>
+      <c r="D21" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-36500</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-154300</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-86500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-89600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-78900</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>16</v>
@@ -1796,40 +1833,43 @@
       <c r="V21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X21" s="3">
         <v>16500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-39400</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AC21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>16</v>
+        <v>200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>16</v>
@@ -1843,23 +1883,23 @@
       <c r="I22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1871,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>100</v>
-      </c>
-      <c r="T22" s="3">
-        <v>200</v>
       </c>
       <c r="U22" s="3">
         <v>200</v>
@@ -1883,156 +1923,162 @@
         <v>200</v>
       </c>
       <c r="W22" s="3">
+        <v>200</v>
+      </c>
+      <c r="X22" s="3">
         <v>300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>2000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>2700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>2400</v>
       </c>
       <c r="AB22" s="3">
         <v>2400</v>
       </c>
       <c r="AC22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AD22" s="3">
         <v>100</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-43800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-38600</v>
       </c>
-      <c r="F23" s="3">
-        <v>-162100</v>
-      </c>
       <c r="G23" s="3">
+        <v>-248800</v>
+      </c>
+      <c r="H23" s="3">
         <v>-100500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-116100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-86700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-123500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1339800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>86000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1336600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>72800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-12700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-6300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-122900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>14600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>106600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
-        <v>-23100</v>
-      </c>
       <c r="G24" s="3">
+        <v>-25400</v>
+      </c>
+      <c r="H24" s="3">
         <v>-20400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-27200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>304400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>49800</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -2064,22 +2110,25 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>13300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2164,180 +2213,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39400</v>
       </c>
-      <c r="F26" s="3">
-        <v>-139000</v>
-      </c>
       <c r="G26" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-80100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-110700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-84400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-96300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>61100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1035500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>65100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1286900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>72800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-10000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-12700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-6300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-122900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>14600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-41900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39400</v>
       </c>
-      <c r="F27" s="3">
-        <v>-139000</v>
-      </c>
       <c r="G27" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="H27" s="3">
         <v>-80100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-110700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-84400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-96300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>61100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1035500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>65100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1286900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>72800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-10000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-122900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>93300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2422,8 +2480,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2508,8 +2569,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2594,8 +2658,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2680,180 +2747,189 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2800</v>
+        <v>2900</v>
       </c>
       <c r="E32" s="3">
-        <v>-29400</v>
+        <v>2800</v>
       </c>
       <c r="F32" s="3">
-        <v>68900</v>
+        <v>29600</v>
       </c>
       <c r="G32" s="3">
-        <v>-12300</v>
+        <v>-11400</v>
       </c>
       <c r="H32" s="3">
-        <v>-2900</v>
+        <v>12200</v>
       </c>
       <c r="I32" s="3">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="J32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-12700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-110200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-147200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-123400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-7000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-41900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39400</v>
       </c>
-      <c r="F33" s="3">
-        <v>-139000</v>
-      </c>
       <c r="G33" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="H33" s="3">
         <v>-80100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-110700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-84400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-96300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>61100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1035500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>65100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1286900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>72800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-10000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-12700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-122900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>93300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2938,185 +3014,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-41900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39400</v>
       </c>
-      <c r="F35" s="3">
-        <v>-139000</v>
-      </c>
       <c r="G35" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="H35" s="3">
         <v>-80100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-110700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-84400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-96300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>61100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1035500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>65100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1286900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>72800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-10000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-12700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-122900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>93300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3232,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3179,77 +3265,78 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71800</v>
+      </c>
+      <c r="E41" s="3">
         <v>66800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>54700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>96200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>40600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>101600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2002700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2640700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2643200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2684300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>241400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>173500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>186200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>41400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>80400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>42200</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3265,8 +3352,11 @@
       <c r="AD41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3274,13 +3364,13 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
@@ -3310,32 +3400,32 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>1200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>8700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>30100</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>51200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>27100</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>1700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>12500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>17200</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3351,77 +3441,80 @@
       <c r="AD42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8200</v>
+        <v>9600</v>
       </c>
       <c r="E43" s="3">
+        <v>59700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1600</v>
       </c>
-      <c r="F43" s="3">
-        <v>3000</v>
-      </c>
       <c r="G43" s="3">
+        <v>58400</v>
+      </c>
+      <c r="H43" s="3">
         <v>9800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>10100</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="J43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" s="3">
         <v>504300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>357900</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>275000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>100</v>
       </c>
       <c r="P43" s="3">
         <v>100</v>
       </c>
       <c r="Q43" s="3">
+        <v>100</v>
+      </c>
+      <c r="R43" s="3">
         <v>1000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>14000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>24800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>23700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>26400</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3437,77 +3530,80 @@
       <c r="AD43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E44" s="3">
         <v>131300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>99200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>142300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>217100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>272100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>310500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1685600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1328900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1626200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1193300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>812400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>118400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>83500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>52400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>31400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>35500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>30200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>60400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>65500</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3523,77 +3619,80 @@
       <c r="AD44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>129700</v>
+      <c r="D45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E45" s="3">
-        <v>165400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>122200</v>
+        <v>74900</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G45" s="3">
-        <v>81700</v>
-      </c>
-      <c r="H45" s="3">
-        <v>83400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>138300</v>
-      </c>
-      <c r="J45" s="3">
+        <v>63100</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" s="3">
         <v>1427300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1335300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1420300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1937600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1501800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>186200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>201800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>82800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>31700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>37000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>40800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>74700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>64800</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3609,77 +3708,80 @@
       <c r="AD45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>307500</v>
+      </c>
+      <c r="E46" s="3">
         <v>336000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>321000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>363700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>349200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>431800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>520800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>555700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5024700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5687200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5774100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5273500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>546200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>458800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>323500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>140200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>101100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>115400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>145900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>144900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>222500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>216100</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3695,13 +3797,16 @@
       <c r="AD46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="E47" s="3">
         <v>2800</v>
@@ -3716,13 +3821,13 @@
         <v>2800</v>
       </c>
       <c r="I47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="J47" s="3">
         <v>2900</v>
       </c>
       <c r="K47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="L47" s="3">
         <v>20000</v>
@@ -3734,11 +3839,11 @@
         <v>20000</v>
       </c>
       <c r="O47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="P47" s="3">
         <v>2800</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -3746,11 +3851,11 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
+        <v>0</v>
+      </c>
+      <c r="T47" s="3">
         <v>400</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3766,8 +3871,8 @@
       <c r="Y47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -3781,77 +3886,80 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E48" s="3">
         <v>46000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>36300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>53400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>717200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>355400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>357200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>340600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>216500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>8200</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3867,58 +3975,61 @@
       <c r="AD48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>70900</v>
+        <v>1000</v>
       </c>
       <c r="E49" s="3">
-        <v>91200</v>
+        <v>1000</v>
       </c>
       <c r="F49" s="3">
-        <v>28300</v>
+        <v>1100</v>
       </c>
       <c r="G49" s="3">
-        <v>30500</v>
+        <v>0</v>
       </c>
       <c r="H49" s="3">
-        <v>28800</v>
+        <v>0</v>
       </c>
       <c r="I49" s="3">
-        <v>13400</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3">
+        <v>0</v>
+      </c>
+      <c r="K49" s="3">
         <v>12500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>74100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>51300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>20300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>900</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -3953,8 +4064,11 @@
       <c r="AD49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4039,8 +4153,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4125,52 +4242,55 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>69900</v>
+        <v>71200</v>
       </c>
       <c r="E52" s="3">
-        <v>67800</v>
+        <v>70300</v>
       </c>
       <c r="F52" s="3">
-        <v>67300</v>
+        <v>90600</v>
       </c>
       <c r="G52" s="3">
-        <v>45400</v>
+        <v>28800</v>
       </c>
       <c r="H52" s="3">
-        <v>21700</v>
+        <v>31800</v>
       </c>
       <c r="I52" s="3">
+        <v>30500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K52" s="3">
         <v>24200</v>
       </c>
-      <c r="J52" s="3">
-        <v>24200</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>107300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>78900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>70600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>102000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>400</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
@@ -4179,23 +4299,23 @@
         <v>400</v>
       </c>
       <c r="T52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="U52" s="3">
         <v>300</v>
       </c>
       <c r="V52" s="3">
+        <v>300</v>
+      </c>
+      <c r="W52" s="3">
         <v>800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4211,8 +4331,11 @@
       <c r="AD52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4297,77 +4420,80 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>502100</v>
+      </c>
+      <c r="E54" s="3">
         <v>525500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>534100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>493300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>464100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>538400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>633700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>685000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5581400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6194700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6250500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5632300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>558400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>465900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>328700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>144300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>106800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>133900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>152500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>152700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>245800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>225300</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4383,8 +4509,11 @@
       <c r="AD54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4415,8 +4544,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4447,77 +4577,78 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E57" s="3">
         <v>29900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>19200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>97000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>143400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>6300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>5200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>10300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9700</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4533,31 +4664,34 @@
       <c r="AD57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4578,32 +4712,32 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>4500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>7200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>28900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>19600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>38300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>30800</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4619,77 +4753,80 @@
       <c r="AD58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>86900</v>
+        <v>96900</v>
       </c>
       <c r="E59" s="3">
-        <v>93800</v>
+        <v>65200</v>
       </c>
       <c r="F59" s="3">
-        <v>128900</v>
+        <v>49500</v>
       </c>
       <c r="G59" s="3">
-        <v>71700</v>
+        <v>99700</v>
       </c>
       <c r="H59" s="3">
-        <v>82800</v>
+        <v>9200</v>
       </c>
       <c r="I59" s="3">
-        <v>56000</v>
+        <v>11900</v>
       </c>
       <c r="J59" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K59" s="3">
         <v>395300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>658600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1379100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2093600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1941700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>188600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>176100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>236300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>9100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>53200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>54400</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4705,77 +4842,80 @@
       <c r="AD59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>151200</v>
+      </c>
+      <c r="E60" s="3">
         <v>116800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>110500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>135200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>110100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>83000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>75300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>691300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1476100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2194800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2085100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>205700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>191400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>247100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>82500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>36300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>45700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>43900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>103000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>94900</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4791,31 +4931,34 @@
       <c r="AD60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>19200</v>
+        <v>25600</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -4877,77 +5020,80 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>11300</v>
+        <v>9400</v>
       </c>
       <c r="E62" s="3">
-        <v>11900</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3">
-        <v>9900</v>
+        <v>9500</v>
       </c>
       <c r="G62" s="3">
-        <v>9800</v>
+        <v>9700</v>
       </c>
       <c r="H62" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="K62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L62" s="3">
+        <v>18700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>16900</v>
+      </c>
+      <c r="N62" s="3">
+        <v>85100</v>
+      </c>
+      <c r="O62" s="3">
+        <v>88500</v>
+      </c>
+      <c r="P62" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>10500</v>
+      </c>
+      <c r="R62" s="3">
+        <v>1200</v>
+      </c>
+      <c r="S62" s="3">
+        <v>1600</v>
+      </c>
+      <c r="T62" s="3">
         <v>2200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="U62" s="3">
         <v>2600</v>
       </c>
-      <c r="J62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>18700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>16900</v>
-      </c>
-      <c r="M62" s="3">
-        <v>85100</v>
-      </c>
-      <c r="N62" s="3">
-        <v>88500</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="V62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="W62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="X62" s="3">
         <v>2700</v>
       </c>
-      <c r="P62" s="3">
-        <v>10500</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1200</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1600</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2200</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2600</v>
-      </c>
-      <c r="U62" s="3">
-        <v>3300</v>
-      </c>
-      <c r="V62" s="3">
-        <v>2100</v>
-      </c>
-      <c r="W62" s="3">
-        <v>2700</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2900</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>16</v>
       </c>
@@ -4963,8 +5109,11 @@
       <c r="AD62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5049,8 +5198,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5135,8 +5287,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5221,77 +5376,80 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>186300</v>
+      </c>
+      <c r="E66" s="3">
         <v>147300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>122400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>145100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>100700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>112300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>85600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>77300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>710000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1492900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2280000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2173600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>208300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>201900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>248300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>84100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>38900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>49000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>46000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>105700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>97800</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5307,8 +5465,11 @@
       <c r="AD66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5339,8 +5500,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5425,8 +5587,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5511,8 +5676,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5597,8 +5765,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5683,77 +5854,80 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-342700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-267100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-225200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-204700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-65700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>125100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>209400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1932800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1886700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1277800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>900800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-65800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-121100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-152700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-152900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-151300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-138500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-144500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-136000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-13100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5769,8 +5943,11 @@
       <c r="AD72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5855,8 +6032,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5941,8 +6121,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6027,77 +6210,80 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>315800</v>
+      </c>
+      <c r="E76" s="3">
         <v>378200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>411700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>348200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>363400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>426100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>548100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>607700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4871400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4701800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3970600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3458700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>350100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>264000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>80500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>60200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>80100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>95000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>103500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>106700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>140100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>127500</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6113,8 +6299,11 @@
       <c r="AD76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6199,185 +6388,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-75600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-41900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39400</v>
       </c>
-      <c r="F81" s="3">
-        <v>-139000</v>
-      </c>
       <c r="G81" s="3">
+        <v>-223400</v>
+      </c>
+      <c r="H81" s="3">
         <v>-80100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-110700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-84400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-96300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>61100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1035500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>65100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1286900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>72800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-10000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-12700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-122900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-41000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>93300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6408,31 +6606,32 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>14900</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -6473,8 +6672,8 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>16</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>16</v>
@@ -6494,8 +6693,11 @@
       <c r="AD83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6580,8 +6782,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6666,8 +6871,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6752,8 +6960,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6838,8 +7049,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6924,8 +7138,11 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6947,15 +7164,15 @@
       <c r="I89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K89" s="3">
         <v>-182600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-582200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>16</v>
       </c>
@@ -6968,8 +7185,8 @@
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
+      <c r="Q89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -6989,8 +7206,8 @@
       <c r="W89" s="3">
         <v>0</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>16</v>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>16</v>
@@ -7010,8 +7227,11 @@
       <c r="AD89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7042,31 +7262,32 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -7107,8 +7328,8 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>16</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>16</v>
@@ -7128,8 +7349,11 @@
       <c r="AD91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7214,8 +7438,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7300,8 +7527,11 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7323,15 +7553,15 @@
       <c r="I94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-40300</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7344,8 +7574,8 @@
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
+      <c r="Q94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -7365,8 +7595,8 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>16</v>
+      <c r="X94" s="3">
+        <v>0</v>
       </c>
       <c r="Y94" s="3" t="s">
         <v>16</v>
@@ -7386,8 +7616,11 @@
       <c r="AD94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7418,31 +7651,32 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7504,8 +7738,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7590,8 +7827,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7676,8 +7916,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7762,8 +8005,11 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7785,15 +8031,15 @@
       <c r="I100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K100" s="3">
         <v>-56200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-315600</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>16</v>
       </c>
@@ -7806,8 +8052,8 @@
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
+      <c r="Q100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R100" s="3">
         <v>0</v>
@@ -7827,8 +8073,8 @@
       <c r="W100" s="3">
         <v>0</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>16</v>
+      <c r="X100" s="3">
+        <v>0</v>
       </c>
       <c r="Y100" s="3" t="s">
         <v>16</v>
@@ -7848,8 +8094,11 @@
       <c r="AD100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7862,8 +8111,8 @@
       <c r="F101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>16</v>
+      <c r="G101" s="3">
+        <v>-110300</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>16</v>
@@ -7871,15 +8120,15 @@
       <c r="I101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K101" s="3">
         <v>-80000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>209000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>16</v>
       </c>
@@ -7892,8 +8141,8 @@
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -7913,8 +8162,8 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>16</v>
+      <c r="X101" s="3">
+        <v>0</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>16</v>
@@ -7934,38 +8183,41 @@
       <c r="AD101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>16</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
       </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-326900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-729000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>16</v>
       </c>
@@ -7978,8 +8230,8 @@
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
+      <c r="Q102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R102" s="3">
         <v>0</v>
@@ -7999,8 +8251,8 @@
       <c r="W102" s="3">
         <v>0</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>16</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>16</v>
@@ -8018,6 +8270,9 @@
         <v>16</v>
       </c>
       <c r="AD102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,404 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>88800</v>
+      </c>
+      <c r="F8" s="3">
         <v>73600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>71900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>35100</v>
       </c>
-      <c r="G8" s="3">
-        <v>104300</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
+        <v>49100</v>
+      </c>
+      <c r="J8" s="3">
         <v>33300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>73900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>55200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>47400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>978200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>3008800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>201800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2184600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>187300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>153800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>56100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>24000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>26200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>10700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>71300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>103300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>37700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>7200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>40300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>69800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>126000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>153300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E9" s="3">
         <v>95100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
+        <v>95100</v>
+      </c>
+      <c r="G9" s="3">
         <v>91000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>72400</v>
       </c>
-      <c r="G9" s="3">
-        <v>205900</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>103100</v>
+      </c>
+      <c r="J9" s="3">
         <v>102400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>143900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>102800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>939900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>744000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1264100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>78300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>696800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>81900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>92900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>29000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>26500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>19900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>10300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>175000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>80700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>36000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>7100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>38600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>62700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>174600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>40600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F10" s="3">
         <v>-21500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-19100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-37300</v>
       </c>
-      <c r="G10" s="3">
-        <v>-101600</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>-54100</v>
+      </c>
+      <c r="J10" s="3">
         <v>-69100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-70100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-47500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-892500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>234200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1744700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>123500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1487800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>105400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>60800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>27000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>-2500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>6400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-103700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>22500</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>1700</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>100</v>
       </c>
       <c r="AA10" s="3">
         <v>1700</v>
       </c>
       <c r="AB10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC10" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AD10" s="3">
         <v>7100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>112800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1085,97 +1110,105 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>16600</v>
+      </c>
+      <c r="F12" s="3">
         <v>14800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>14600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>15300</v>
       </c>
-      <c r="G12" s="3">
-        <v>29800</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
+        <v>10800</v>
+      </c>
+      <c r="J12" s="3">
         <v>17200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>17900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>19100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>32800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>118100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>205100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>15200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>117900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>13200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>9900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>8100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="U12" s="3">
         <v>5600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>4700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="W12" s="3">
         <v>3800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="X12" s="3">
         <v>6500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="Y12" s="3">
         <v>9600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Z12" s="3">
         <v>5700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>5600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AB12" s="3">
         <v>4800</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>7400</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AD12" s="3">
         <v>9800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>5500</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AF12" s="3">
         <v>4700</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AG12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1263,64 +1296,70 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E14" s="3">
+        <v>18900</v>
+      </c>
+      <c r="F14" s="3">
         <v>34800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
-        <v>80300</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
+        <v>65500</v>
+      </c>
+      <c r="J14" s="3">
         <v>5700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>9100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" s="3">
         <v>67200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>11300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>30400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>16</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1352,38 +1391,44 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>14900</v>
+        <v>7100</v>
       </c>
       <c r="E15" s="3">
-        <v>6500</v>
+        <v>7100</v>
       </c>
       <c r="F15" s="3">
         <v>14900</v>
       </c>
       <c r="G15" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>14900</v>
+      </c>
+      <c r="J15" s="3">
         <v>8400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>17600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>8200</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1393,11 +1438,11 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>16</v>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>16</v>
@@ -1414,35 +1459,41 @@
       <c r="V15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="3">
         <v>500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>400</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>120900</v>
+      </c>
+      <c r="E17" s="3">
+        <v>147600</v>
+      </c>
+      <c r="F17" s="3">
         <v>124000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>117700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>103100</v>
       </c>
-      <c r="G17" s="3">
-        <v>262100</v>
-      </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
+        <v>136000</v>
+      </c>
+      <c r="J17" s="3">
         <v>140500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>183800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>140900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>183600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1030300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1816100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>116300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>971300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>121400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>130200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>58000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>15200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>37700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>29000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>21800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>194700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>91900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>79600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>16100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>51200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>79700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>188800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>51000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-38100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-50400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-45800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-68000</v>
       </c>
-      <c r="G18" s="3">
-        <v>-157800</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="J18" s="3">
         <v>-107200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-110000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-85700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-136200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-52100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>1192700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>85500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>1213300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>65900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>23500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-9900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-13700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-2800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-11100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-123400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>11300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-42000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>102400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1682,127 +1747,135 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-70200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-2900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-2800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-29600</v>
       </c>
-      <c r="G20" s="3">
-        <v>11400</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J20" s="3">
         <v>-12200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>12700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>110200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>147200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>123400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>7000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>5100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>3600</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>500</v>
       </c>
       <c r="AA20" s="3">
         <v>1500</v>
       </c>
       <c r="AB20" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD20" s="3">
         <v>1800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>9800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>4300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-32500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-36500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-23500</v>
       </c>
-      <c r="G21" s="3">
-        <v>-154300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>-81900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-86500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-89600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-78900</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1836,46 +1909,52 @@
       <c r="W21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z21" s="3">
         <v>16500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-39400</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AE21" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>300</v>
+      </c>
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>16</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>16</v>
@@ -1886,8 +1965,8 @@
       <c r="J22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>16</v>
@@ -1895,17 +1974,17 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>16</v>
+      <c r="N22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -1914,177 +1993,189 @@
         <v>0</v>
       </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>100</v>
-      </c>
-      <c r="U22" s="3">
-        <v>200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>200</v>
       </c>
       <c r="W22" s="3">
         <v>200</v>
       </c>
       <c r="X22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>200</v>
+      </c>
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>2000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>2700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>2400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>2400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>100</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-85700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-82300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-43800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-38600</v>
       </c>
-      <c r="G23" s="3">
-        <v>-248800</v>
-      </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
+        <v>-162100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-116100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-86700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-123500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>58000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1339800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>86000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>1336600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>72800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>24000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-10000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-12700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-122900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>14600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>106600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>85300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-6700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
-        <v>-25400</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="J24" s="3">
         <v>-20400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-5500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-27200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-3000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>304400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>20900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>49800</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -2113,22 +2204,28 @@
         <v>0</v>
       </c>
       <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>6700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>13300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-75600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-41900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-39400</v>
       </c>
-      <c r="G26" s="3">
-        <v>-223400</v>
-      </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="J26" s="3">
         <v>-80100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-110700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-84400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-96300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>61100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1035500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>65100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1286900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>72800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>23900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-10000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-12700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-6300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-122900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>14600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>93300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-75600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-41900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-39400</v>
       </c>
-      <c r="G27" s="3">
-        <v>-223400</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="J27" s="3">
         <v>-80100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-110700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-84400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-96300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>61100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1035500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>65100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1286900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>72800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>23900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-10000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-12700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-6300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-122900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>14600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>93300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E32" s="3">
+        <v>70200</v>
+      </c>
+      <c r="F32" s="3">
         <v>2900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>2800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>29600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="J32" s="3">
         <v>12200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-12700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-110200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-147200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-123400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-7000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-5100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-3600</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-500</v>
       </c>
       <c r="AA32" s="3">
         <v>-1500</v>
       </c>
       <c r="AB32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="F33" s="3">
         <v>-75600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-41900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-39400</v>
       </c>
-      <c r="G33" s="3">
-        <v>-223400</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="J33" s="3">
         <v>-80100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-110700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-84400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-96300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>61100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1035500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>65100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1286900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>72800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>23900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-10000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-12700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-6300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-122900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>14600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>93300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="F35" s="3">
         <v>-75600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-41900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-39400</v>
       </c>
-      <c r="G35" s="3">
-        <v>-223400</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="J35" s="3">
         <v>-80100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-110700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-84400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-96300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>61100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1035500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>65100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1286900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>72800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>23900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-10000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-12700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-6300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-122900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>14600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>93300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,83 +3437,85 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>96500</v>
+      </c>
+      <c r="F41" s="3">
         <v>71800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>66800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>54700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>96200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>40600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>66100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>72000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>101600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2002700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2640700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2643200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2684300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>241400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>173500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>186200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>54500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>26100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>23100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>41400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>80400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>51200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>42200</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3355,8 +3528,14 @@
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3364,20 +3543,20 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>3300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>3700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -3403,35 +3582,35 @@
         <v>0</v>
       </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>1200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>8700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>30100</v>
       </c>
-      <c r="U42" s="3">
+      <c r="W42" s="3">
         <v>51200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="X42" s="3">
         <v>27100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="Y42" s="3">
         <v>1700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>12500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>17200</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3444,83 +3623,89 @@
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62600</v>
+      </c>
+      <c r="E43" s="3">
+        <v>114700</v>
+      </c>
+      <c r="F43" s="3">
         <v>9600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>59700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>58400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>9800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>10100</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M43" s="3">
         <v>504300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>357900</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
         <v>275000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>14000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>24800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>23700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>26400</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3533,83 +3718,89 @@
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>113900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>94600</v>
+      </c>
+      <c r="F44" s="3">
         <v>87800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>131300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>99200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>142300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>217100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>272100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>310500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1685600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1328900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1626200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1193300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>812400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>118400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>83500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>52400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>31400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>7900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>13000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>35500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>30200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>60400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>65500</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3622,8 +3813,14 @@
       <c r="AE44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3631,74 +3828,74 @@
         <v>16</v>
       </c>
       <c r="E45" s="3">
+        <v>26100</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="3">
         <v>74900</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>63100</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M45" s="3">
         <v>1427300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1335300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1420300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1937600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1501800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>186200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>201800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>82800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>31700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>37000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>26600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>40800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>7700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>74700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>64800</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3711,83 +3908,89 @@
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>435200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>334000</v>
+      </c>
+      <c r="F46" s="3">
         <v>307500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>336000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>321000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>363700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>349200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>431800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>520800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>555700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5024700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5687200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>5774100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>5273500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>546200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>458800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>323500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>140200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>101100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>115400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>145900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>144900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>222500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>216100</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB46" s="3" t="s">
         <v>16</v>
       </c>
@@ -3800,19 +4003,25 @@
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="E47" s="3">
         <v>2800</v>
       </c>
       <c r="F47" s="3">
-        <v>2800</v>
+        <v>2900</v>
       </c>
       <c r="G47" s="3">
         <v>2800</v>
@@ -3824,16 +4033,16 @@
         <v>2800</v>
       </c>
       <c r="J47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="K47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="L47" s="3">
         <v>2900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>2900</v>
-      </c>
-      <c r="L47" s="3">
-        <v>20000</v>
-      </c>
-      <c r="M47" s="3">
-        <v>20000</v>
       </c>
       <c r="N47" s="3">
         <v>20000</v>
@@ -3842,26 +4051,26 @@
         <v>20000</v>
       </c>
       <c r="P47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="R47" s="3">
         <v>2800</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
       <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
         <v>400</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>16</v>
       </c>
@@ -3874,11 +4083,11 @@
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
@@ -3889,83 +4098,89 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>44000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>43700</v>
+      </c>
+      <c r="F48" s="3">
         <v>43500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>46000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>51300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>31200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>36300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>53400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>72400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>717200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>355400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>357200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>340600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>216500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>8100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>6600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>4800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>3700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>4900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>18200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>6300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>7000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>21200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>8200</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB48" s="3" t="s">
         <v>16</v>
       </c>
@@ -3978,26 +4193,32 @@
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>900</v>
+      </c>
+      <c r="F49" s="3">
         <v>1000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>1000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>1100</v>
       </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
@@ -4005,37 +4226,37 @@
         <v>0</v>
       </c>
       <c r="K49" s="3">
+        <v>0</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3">
         <v>12500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>74100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>51300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>45300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>20300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>900</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
-      </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -4067,8 +4288,14 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,83 +4478,89 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>81400</v>
+      </c>
+      <c r="F52" s="3">
         <v>71200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>70300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>90600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>28800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>31800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>30500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>16100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>24200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>107300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>78900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>70600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>102000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>500</v>
       </c>
       <c r="R52" s="3">
         <v>400</v>
       </c>
       <c r="S52" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="T52" s="3">
         <v>400</v>
       </c>
       <c r="U52" s="3">
+        <v>400</v>
+      </c>
+      <c r="V52" s="3">
+        <v>400</v>
+      </c>
+      <c r="W52" s="3">
         <v>300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>2000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>1000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4334,8 +4573,14 @@
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,83 +4668,89 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>565600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>463000</v>
+      </c>
+      <c r="F54" s="3">
         <v>502100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>525500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>534100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>493300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>464100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>538400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>633700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>685000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>5581400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>6194700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>6250500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>5632300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>558400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>465900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>328700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>144300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>106800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>133900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>152500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>152700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>245800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>225300</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4512,8 +4763,14 @@
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,83 +4837,85 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>16700</v>
+        <v>15700</v>
       </c>
       <c r="E57" s="3">
-        <v>29900</v>
+        <v>14000</v>
       </c>
       <c r="F57" s="3">
         <v>16700</v>
       </c>
       <c r="G57" s="3">
+        <v>29900</v>
+      </c>
+      <c r="H57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="I57" s="3">
         <v>6200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>19200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>27300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>26900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>16700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>32700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>97000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>101200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>143400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>17100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>15300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>2400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>10300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>15300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>11500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>9700</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4667,38 +4928,44 @@
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>17900</v>
+      </c>
+      <c r="F58" s="3">
         <v>1400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1500</v>
-      </c>
-      <c r="F58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1200</v>
       </c>
       <c r="H58" s="3">
         <v>1600</v>
       </c>
       <c r="I58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K58" s="3">
         <v>1900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2400</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4715,35 +4982,35 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>4500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>6800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>7200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>28900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>29700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>19600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>38300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>30800</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>16</v>
       </c>
@@ -4756,83 +5023,89 @@
       <c r="AE58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>212100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>122200</v>
+      </c>
+      <c r="F59" s="3">
         <v>96900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>65200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>49500</v>
       </c>
-      <c r="G59" s="3">
-        <v>99700</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
+        <v>99600</v>
+      </c>
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>11900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>15600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>395300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>658600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1379100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2093600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1941700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>188600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>176100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>236300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>70500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>15800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>5100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>5700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>9100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>53200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>54400</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>16</v>
       </c>
@@ -4845,83 +5118,89 @@
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>289900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>178600</v>
+      </c>
+      <c r="F60" s="3">
         <v>151200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>116800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>110500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>135200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>90900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>110100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>83000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>75300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>691300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1476100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2194800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>2085100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>205700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>191400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>247100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>82500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>24500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>36300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>45700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>43900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>103000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>94900</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB60" s="3" t="s">
         <v>16</v>
       </c>
@@ -4934,38 +5213,44 @@
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F61" s="3">
         <v>25600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>21000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>700</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -5023,83 +5308,89 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3">
         <v>9400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>9500</v>
       </c>
-      <c r="G62" s="3">
-        <v>9700</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>500</v>
+      </c>
+      <c r="J62" s="3">
         <v>9400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>18700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>16900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>85100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>88500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>10500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>1200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>1600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>3300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2900</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5112,8 +5403,14 @@
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,83 +5688,89 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>320900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>196800</v>
+      </c>
+      <c r="F66" s="3">
         <v>186300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>147300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>122400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>145100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>100700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>112300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>85600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>77300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>710000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1492900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>2280000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>2173600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>208300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>201900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>248300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>84100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>26700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>38900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>49000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>46000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>105700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>97800</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5468,8 +5783,14 @@
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,83 +6198,89 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-522000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-435600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-342700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-267100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-225200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-204700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-65700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>14400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>125100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>209400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1932800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1886700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1277800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>900800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-65800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-121100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-152700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-152900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-151300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-138500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-144500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-136000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-13100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB72" s="3" t="s">
         <v>16</v>
       </c>
@@ -5946,8 +6293,14 @@
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,83 +6578,89 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>244600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>266300</v>
+      </c>
+      <c r="F76" s="3">
         <v>315800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>378200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>411700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>348200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>363400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>426100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>548100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>607700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4871400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4701800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3970600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3458700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>350100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>264000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>80500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>60200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>80100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>95000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>103500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>106700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>140100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>127500</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6302,8 +6673,14 @@
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-92900</v>
+      </c>
+      <c r="F81" s="3">
         <v>-75600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-41900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-39400</v>
       </c>
-      <c r="G81" s="3">
-        <v>-223400</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
+        <v>-139000</v>
+      </c>
+      <c r="J81" s="3">
         <v>-80100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-110700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-84400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-96300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>61100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1035500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>65100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1286900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>72800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>23900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-10000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-12700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-6300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-122900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>14600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-41000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-10400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>93300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,8 +7002,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6621,23 +7018,23 @@
       <c r="F83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="3">
         <v>14900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -6675,11 +7072,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z83" s="3" t="s">
-        <v>16</v>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="3">
+        <v>0</v>
       </c>
       <c r="AA83" s="3" t="s">
         <v>16</v>
@@ -6696,8 +7093,14 @@
       <c r="AE83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,8 +7568,14 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7167,18 +7600,18 @@
       <c r="J89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M89" s="3">
         <v>-182600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-582200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7188,11 +7621,11 @@
       <c r="Q89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="R89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T89" s="3">
         <v>0</v>
@@ -7209,11 +7642,11 @@
       <c r="X89" s="3">
         <v>0</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z89" s="3" t="s">
-        <v>16</v>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="3">
+        <v>0</v>
       </c>
       <c r="AA89" s="3" t="s">
         <v>16</v>
@@ -7230,8 +7663,14 @@
       <c r="AE89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,8 +7702,10 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7289,11 +7730,11 @@
       <c r="J91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -7331,11 +7772,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>16</v>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>0</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>16</v>
@@ -7352,8 +7793,14 @@
       <c r="AE91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,8 +7983,14 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -7556,18 +8015,18 @@
       <c r="J94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M94" s="3">
         <v>-8100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-40300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>16</v>
       </c>
@@ -7577,11 +8036,11 @@
       <c r="Q94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="R94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T94" s="3">
         <v>0</v>
@@ -7598,11 +8057,11 @@
       <c r="X94" s="3">
         <v>0</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>16</v>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>16</v>
@@ -7619,8 +8078,14 @@
       <c r="AE94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,8 +8117,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7678,11 +8145,11 @@
       <c r="J96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7741,8 +8208,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,8 +8493,14 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8034,18 +8525,18 @@
       <c r="J100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M100" s="3">
         <v>-56200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-315600</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8055,11 +8546,11 @@
       <c r="Q100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="R100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T100" s="3">
         <v>0</v>
@@ -8076,11 +8567,11 @@
       <c r="X100" s="3">
         <v>0</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z100" s="3" t="s">
-        <v>16</v>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
+        <v>0</v>
       </c>
       <c r="AA100" s="3" t="s">
         <v>16</v>
@@ -8097,8 +8588,14 @@
       <c r="AE100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8111,30 +8608,30 @@
       <c r="F101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="3">
         <v>-110300</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="M101" s="3">
         <v>-80000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>209000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8144,11 +8641,11 @@
       <c r="Q101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -8165,11 +8662,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z101" s="3" t="s">
-        <v>16</v>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>0</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>16</v>
@@ -8186,8 +8683,14 @@
       <c r="AE101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8213,17 +8716,17 @@
         <v>0</v>
       </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-326900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-729000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8233,11 +8736,11 @@
       <c r="Q102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="R102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="T102" s="3">
         <v>0</v>
@@ -8254,11 +8757,11 @@
       <c r="X102" s="3">
         <v>0</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Z102" s="3" t="s">
-        <v>16</v>
+      <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
+        <v>0</v>
       </c>
       <c r="AA102" s="3" t="s">
         <v>16</v>
@@ -8273,6 +8776,12 @@
         <v>16</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,429 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>82800</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3">
         <v>88800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>73600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>71900</v>
       </c>
-      <c r="H8" s="3">
-        <v>35100</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="I8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="3">
         <v>49100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>73900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>55200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>47400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>978200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3008800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>201800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2184600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>187300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>153800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>56100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>24000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>26200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>10700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>71300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>103300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>37700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>7200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>40300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>69800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>126000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>153300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>82100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>95100</v>
+      <c r="D9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="F9" s="3">
         <v>95100</v>
       </c>
       <c r="G9" s="3">
+        <v>95100</v>
+      </c>
+      <c r="H9" s="3">
         <v>91000</v>
       </c>
-      <c r="H9" s="3">
-        <v>72400</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="I9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="3">
         <v>103100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>143900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>939900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>744000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1264100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>78300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>696800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>81900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>92900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>29000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>175000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>80700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>36000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>38600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>62700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>174600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>40600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>600</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="3">
         <v>-6400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-21500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-19100</v>
       </c>
-      <c r="H10" s="3">
-        <v>-37300</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="I10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="3">
         <v>-54100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-69100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-70100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-47500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-892500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>234200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1744700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>123500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1487800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>105400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>60800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>27000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-2500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>6400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-103700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>112800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,103 +1125,107 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
-        <v>18900</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="3">
         <v>16600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>14800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14600</v>
       </c>
-      <c r="H12" s="3">
-        <v>15300</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="3">
         <v>10800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>17900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>19100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>32800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>118100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>205100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>117900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>13200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>9900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>8100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>4700</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>6500</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>9600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>4800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>7400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>9800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>5500</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>4700</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1302,58 +1319,61 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
-        <v>27700</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="3">
         <v>18900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>34800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>800</v>
       </c>
-      <c r="H14" s="3">
-        <v>400</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="3">
         <v>65500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>9100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="3">
         <v>67200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>30400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
+      <c r="R14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>16</v>
@@ -1361,8 +1381,8 @@
       <c r="U14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1397,41 +1417,44 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
         <v>7100</v>
       </c>
-      <c r="E15" s="3">
-        <v>7100</v>
-      </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>14900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>14900</v>
       </c>
-      <c r="I15" s="3">
-        <v>14900</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>17600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8200</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1444,8 +1467,8 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>16</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>16</v>
@@ -1465,15 +1488,15 @@
       <c r="X15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z15" s="3">
         <v>500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>400</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AB15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1483,8 +1506,8 @@
       <c r="AD15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1492,8 +1515,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1550,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
-        <v>120900</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3">
         <v>147600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>124000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>117700</v>
       </c>
-      <c r="H17" s="3">
-        <v>103100</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="I17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="3">
         <v>136000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>183800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>183600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1030300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1816100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>116300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>971300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>121400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>130200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>58000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>15200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>37700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>29000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>194700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>91900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>79600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>16100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>51200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>79700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>188800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>51000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="3">
-        <v>-38100</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="3">
         <v>-58800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-50400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-45800</v>
       </c>
-      <c r="H18" s="3">
-        <v>-68000</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="I18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="3">
         <v>-86900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-107200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-110000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-85700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-136200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-52100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1192700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>85500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1213300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>65900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-9900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-13700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-123400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>102400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1749,136 +1782,140 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
-        <v>19600</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="3">
         <v>-70200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2800</v>
       </c>
-      <c r="H20" s="3">
-        <v>-29600</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="3">
         <v>9900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>12700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>110200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>147200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>123400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>7000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>5100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-50700</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>18500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-32500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-36500</v>
       </c>
-      <c r="H21" s="3">
-        <v>-23500</v>
-      </c>
       <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-81900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-86500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-89600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-78900</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1915,49 +1952,52 @@
       <c r="Y21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA21" s="3">
         <v>16500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-39400</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>400</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="3">
         <v>300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>200</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
+      <c r="H22" s="3">
+        <v>0</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>16</v>
@@ -1971,23 +2011,23 @@
       <c r="L22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1999,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
         <v>100</v>
-      </c>
-      <c r="W22" s="3">
-        <v>200</v>
       </c>
       <c r="X22" s="3">
         <v>200</v>
@@ -2011,174 +2051,180 @@
         <v>200</v>
       </c>
       <c r="Z22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>2000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>2700</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>2400</v>
       </c>
       <c r="AE22" s="3">
         <v>2400</v>
       </c>
       <c r="AF22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AG22" s="3">
         <v>100</v>
       </c>
-      <c r="AG22" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-85700</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-82300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-43800</v>
       </c>
-      <c r="H23" s="3">
-        <v>-38600</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="I23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="3">
         <v>-162100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-116100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-86700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-123500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>58000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1339800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>86000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1336600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>72800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>24000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-12700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-2500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>14600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-12100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>106600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>700</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="3">
         <v>85300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-6700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1900</v>
       </c>
-      <c r="H24" s="3">
-        <v>800</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="I24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="3">
         <v>-23100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-20400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-27200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>304400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>49800</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
@@ -2210,22 +2256,25 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>13300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2368,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="3">
         <v>-92900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-75600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-41900</v>
       </c>
-      <c r="H26" s="3">
-        <v>-39400</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="I26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J26" s="3">
         <v>-139000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-80100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-110700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-84400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-96300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>61100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1035500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>65100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1286900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>72800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-10000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-12700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>14600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>93300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="3">
         <v>-92900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-75600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41900</v>
       </c>
-      <c r="H27" s="3">
-        <v>-39400</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="I27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J27" s="3">
         <v>-139000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-80100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-110700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-84400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-96300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>61100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1035500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>65100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1286900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>72800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-10000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-2500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>14600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>93300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2662,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2699,8 +2760,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2858,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,198 +2956,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-19600</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="3">
         <v>70200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2800</v>
       </c>
-      <c r="H32" s="3">
-        <v>29600</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="3">
         <v>-9900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-12700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-110200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-147200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-123400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-7000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="E33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="3">
         <v>-92900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-75600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-41900</v>
       </c>
-      <c r="H33" s="3">
-        <v>-39400</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="I33" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="3">
         <v>-139000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-80100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-110700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-96300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>61100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1035500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>65100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1286900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>72800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-10000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-12700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>14600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>93300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3250,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="3">
         <v>-92900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-75600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-41900</v>
       </c>
-      <c r="H35" s="3">
-        <v>-39400</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="I35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="3">
         <v>-139000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-80100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-110700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-96300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>61100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1035500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>65100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1286900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>72800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-10000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-12700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>14600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>93300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3489,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,86 +3525,87 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
-        <v>96800</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="3">
         <v>96500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>66800</v>
       </c>
-      <c r="H41" s="3">
-        <v>54700</v>
-      </c>
-      <c r="I41" s="3">
+      <c r="I41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J41" s="3">
         <v>96200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>66100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2002700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2640700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2643200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2684300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>241400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>173500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>186200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>26100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>23100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>41400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>80400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>51200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>42200</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3534,8 +3621,11 @@
       <c r="AG41" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH41" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3543,23 +3633,23 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>2200</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>3300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>3700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3588,32 +3678,32 @@
         <v>0</v>
       </c>
       <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
         <v>1200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>30100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>51200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>27100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1700</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>12500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>17200</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3629,86 +3719,89 @@
       <c r="AG42" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>62600</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F43" s="3">
         <v>114700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>59700</v>
       </c>
-      <c r="H43" s="3">
-        <v>1600</v>
-      </c>
-      <c r="I43" s="3">
+      <c r="I43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" s="3">
         <v>58400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>10100</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="M43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N43" s="3">
         <v>504300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>357900</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
       <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>275000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>100</v>
       </c>
       <c r="S43" s="3">
         <v>100</v>
       </c>
       <c r="T43" s="3">
+        <v>100</v>
+      </c>
+      <c r="U43" s="3">
         <v>1000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>14000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>24800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>23700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>26400</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3724,86 +3817,89 @@
       <c r="AG43" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>113900</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="3">
         <v>94600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>87800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>131300</v>
       </c>
-      <c r="H44" s="3">
-        <v>99200</v>
-      </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J44" s="3">
         <v>142300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>217100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>272100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>310500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1685600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1328900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1626200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1193300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>812400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>118400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>83500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>52400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>31400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>13000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>35500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>30200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>60400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>65500</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC44" s="3" t="s">
         <v>16</v>
       </c>
@@ -3819,86 +3915,89 @@
       <c r="AG44" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3">
         <v>26100</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H45" s="3">
         <v>74900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J45" s="3">
         <v>63100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N45" s="3">
         <v>1427300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1335300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1420300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1937600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1501800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>186200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>201800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>82800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>31700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>37000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>26600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>74700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>64800</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>16</v>
       </c>
@@ -3914,86 +4013,89 @@
       <c r="AG45" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
-        <v>435200</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="3">
         <v>334000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>307500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>336000</v>
       </c>
-      <c r="H46" s="3">
-        <v>321000</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="I46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J46" s="3">
         <v>363700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>349200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>431800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>520800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>555700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5024700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5687200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5774100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5273500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>546200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>458800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>323500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>140200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>101100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>115400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>145900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>144900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>222500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>216100</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4009,28 +4111,31 @@
       <c r="AG46" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="3">
         <v>2800</v>
       </c>
-      <c r="E47" s="3">
-        <v>2800</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>2800</v>
       </c>
       <c r="H47" s="3">
         <v>2800</v>
       </c>
-      <c r="I47" s="3">
-        <v>2800</v>
+      <c r="I47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J47" s="3">
         <v>2800</v>
@@ -4039,13 +4144,13 @@
         <v>2800</v>
       </c>
       <c r="L47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="M47" s="3">
         <v>2900</v>
       </c>
       <c r="N47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="O47" s="3">
         <v>20000</v>
@@ -4057,11 +4162,11 @@
         <v>20000</v>
       </c>
       <c r="R47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="S47" s="3">
         <v>2800</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
       <c r="T47" s="3">
         <v>0</v>
       </c>
@@ -4069,11 +4174,11 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
         <v>400</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4089,8 +4194,8 @@
       <c r="AB47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AC47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4104,86 +4209,89 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>44000</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="3">
         <v>43700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46000</v>
       </c>
-      <c r="H48" s="3">
-        <v>51300</v>
-      </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J48" s="3">
         <v>31200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>53400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>72400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>717200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>355400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>357200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>340600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>216500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>18200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>21200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>8200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4199,28 +4307,31 @@
       <c r="AG48" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH48" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>800</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="3">
         <v>900</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1000</v>
       </c>
       <c r="G49" s="3">
         <v>1000</v>
       </c>
       <c r="H49" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+        <v>1000</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -4232,34 +4343,34 @@
         <v>0</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>12500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>74100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>51300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>45300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>20300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>900</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -4294,8 +4405,11 @@
       <c r="AG49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4503,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,61 +4601,64 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>82500</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="3">
         <v>81400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>71200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>70300</v>
       </c>
-      <c r="H52" s="3">
-        <v>90600</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" s="3">
         <v>28800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>24200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>107300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>78900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>70600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>102000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>500</v>
-      </c>
-      <c r="T52" s="3">
-        <v>400</v>
       </c>
       <c r="U52" s="3">
         <v>400</v>
@@ -4547,23 +4667,23 @@
         <v>400</v>
       </c>
       <c r="W52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="X52" s="3">
         <v>300</v>
       </c>
       <c r="Y52" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z52" s="3">
         <v>800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4579,8 +4699,11 @@
       <c r="AG52" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,86 +4797,89 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
-        <v>565600</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="3">
         <v>463000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>502100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>525500</v>
       </c>
-      <c r="H54" s="3">
-        <v>534100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="I54" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" s="3">
         <v>493300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>464100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>538400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>633700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>685000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5581400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6194700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6250500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5632300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>558400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>465900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>328700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>144300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>106800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>133900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>152500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>152700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>245800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>225300</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>16</v>
       </c>
@@ -4769,8 +4895,11 @@
       <c r="AG54" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH54" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4933,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,86 +4969,87 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>15700</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F57" s="3">
         <v>14000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J57" s="3">
+        <v>6200</v>
+      </c>
+      <c r="K57" s="3">
+        <v>19200</v>
+      </c>
+      <c r="L57" s="3">
+        <v>27300</v>
+      </c>
+      <c r="M57" s="3">
+        <v>26900</v>
+      </c>
+      <c r="N57" s="3">
         <v>16700</v>
       </c>
-      <c r="I57" s="3">
-        <v>6200</v>
-      </c>
-      <c r="J57" s="3">
-        <v>19200</v>
-      </c>
-      <c r="K57" s="3">
-        <v>27300</v>
-      </c>
-      <c r="L57" s="3">
-        <v>26900</v>
-      </c>
-      <c r="M57" s="3">
-        <v>16700</v>
-      </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>97000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>143400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>10300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>11500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>9700</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC57" s="3" t="s">
         <v>16</v>
       </c>
@@ -4934,41 +5065,44 @@
       <c r="AG57" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>25400</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F58" s="3">
         <v>17900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="I58" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J58" s="3">
-        <v>1600</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4988,32 +5122,32 @@
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>4500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>28900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>29700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>19600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>38300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>30800</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5029,86 +5163,89 @@
       <c r="AG58" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>212100</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="3">
         <v>122200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>96900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>65200</v>
       </c>
-      <c r="H59" s="3">
-        <v>49500</v>
-      </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" s="3">
         <v>99600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>395300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>658600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1379100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2093600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1941700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>188600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>176100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>236300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>70500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>9100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>53200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>54400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5124,86 +5261,89 @@
       <c r="AG59" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>289900</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="3">
         <v>178600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>151200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>116800</v>
       </c>
-      <c r="H60" s="3">
-        <v>110500</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="I60" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J60" s="3">
         <v>135200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>83000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>75300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>691300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1476100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2194800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2085100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>205700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>191400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>247100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>82500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>36300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>45700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>43900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>103000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>94900</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5219,41 +5359,44 @@
       <c r="AG60" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>21800</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3">
         <v>9000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>25600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>21000</v>
       </c>
-      <c r="H61" s="3">
-        <v>2100</v>
-      </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>700</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -5314,86 +5457,89 @@
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>9100</v>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="3">
         <v>9400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>200</v>
       </c>
-      <c r="H62" s="3">
-        <v>9500</v>
-      </c>
-      <c r="I62" s="3">
+      <c r="I62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>18700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>85100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>88500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>10500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>3300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5409,8 +5555,11 @@
       <c r="AG62" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5653,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5751,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,86 +5849,89 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
-        <v>320900</v>
-      </c>
-      <c r="E66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F66" s="3">
         <v>196800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>186300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>147300</v>
       </c>
-      <c r="H66" s="3">
-        <v>122400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="I66" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J66" s="3">
         <v>145100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>85600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>710000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1492900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2280000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2173600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>208300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>201900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>248300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>84100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>38900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>49000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>46000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>105700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>97800</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC66" s="3" t="s">
         <v>16</v>
       </c>
@@ -5789,8 +5947,11 @@
       <c r="AG66" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH66" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5985,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6081,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6179,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6277,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,86 +6375,89 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-522000</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="3">
         <v>-435600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-342700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-267100</v>
       </c>
-      <c r="H72" s="3">
-        <v>-225200</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" s="3">
         <v>-204700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>125100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>209400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1932800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1886700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1277800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>900800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-65800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-121100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-152700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-152900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-151300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-138500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-144500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-136000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-13100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6299,8 +6473,11 @@
       <c r="AG72" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6571,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6669,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,86 +6767,89 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
-        <v>244600</v>
-      </c>
-      <c r="E76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F76" s="3">
         <v>266300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>315800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>378200</v>
       </c>
-      <c r="H76" s="3">
-        <v>411700</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="I76" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" s="3">
         <v>348200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>363400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>426100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>548100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>607700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4871400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4701800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3970600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3458700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>350100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>264000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>80500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>60200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>80100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>95000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>103500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>106700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>140100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>127500</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AC76" s="3" t="s">
         <v>16</v>
       </c>
@@ -6679,8 +6865,11 @@
       <c r="AG76" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH76" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6963,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-86400</v>
-      </c>
-      <c r="E81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" s="3">
         <v>-92900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-75600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-41900</v>
       </c>
-      <c r="H81" s="3">
-        <v>-39400</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="I81" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" s="3">
         <v>-139000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-80100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-110700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-96300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>61100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1035500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>65100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1286900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>72800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-10000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-12700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-122900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>14600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>93300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,8 +7202,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7024,20 +7223,20 @@
       <c r="H83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3">
         <v>14900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -7078,8 +7277,8 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-      <c r="AA83" s="3" t="s">
-        <v>16</v>
+      <c r="AA83" s="3">
+        <v>0</v>
       </c>
       <c r="AB83" s="3" t="s">
         <v>16</v>
@@ -7099,8 +7298,11 @@
       <c r="AG83" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7396,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7494,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7592,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7690,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,8 +7788,11 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -7606,15 +7823,15 @@
       <c r="L89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N89" s="3">
         <v>-182600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-582200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>16</v>
       </c>
@@ -7627,8 +7844,8 @@
       <c r="S89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T89" s="3">
-        <v>0</v>
+      <c r="T89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U89" s="3">
         <v>0</v>
@@ -7648,8 +7865,8 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>16</v>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>16</v>
@@ -7669,8 +7886,11 @@
       <c r="AG89" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,8 +7924,9 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7736,8 +7957,8 @@
       <c r="L91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -7778,8 +7999,8 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>16</v>
+      <c r="AA91" s="3">
+        <v>0</v>
       </c>
       <c r="AB91" s="3" t="s">
         <v>16</v>
@@ -7799,8 +8020,11 @@
       <c r="AG91" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8118,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,8 +8216,11 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8021,15 +8251,15 @@
       <c r="L94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N94" s="3">
         <v>-8100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-40300</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8042,8 +8272,8 @@
       <c r="S94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
+      <c r="T94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U94" s="3">
         <v>0</v>
@@ -8063,8 +8293,8 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>16</v>
+      <c r="AA94" s="3">
+        <v>0</v>
       </c>
       <c r="AB94" s="3" t="s">
         <v>16</v>
@@ -8084,8 +8314,11 @@
       <c r="AG94" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH94" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8352,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8151,8 +8385,8 @@
       <c r="L96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -8214,8 +8448,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8546,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8644,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,8 +8742,11 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8531,15 +8777,15 @@
       <c r="L100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N100" s="3">
         <v>-56200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-315600</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>16</v>
       </c>
@@ -8552,8 +8798,8 @@
       <c r="S100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
+      <c r="T100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U100" s="3">
         <v>0</v>
@@ -8573,8 +8819,8 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>16</v>
+      <c r="AA100" s="3">
+        <v>0</v>
       </c>
       <c r="AB100" s="3" t="s">
         <v>16</v>
@@ -8594,8 +8840,11 @@
       <c r="AG100" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH100" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8614,27 +8863,27 @@
       <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3">
         <v>-110300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="K101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N101" s="3">
         <v>-80000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>209000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>16</v>
       </c>
@@ -8647,8 +8896,8 @@
       <c r="S101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -8668,8 +8917,8 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-      <c r="AA101" s="3" t="s">
-        <v>16</v>
+      <c r="AA101" s="3">
+        <v>0</v>
       </c>
       <c r="AB101" s="3" t="s">
         <v>16</v>
@@ -8689,8 +8938,11 @@
       <c r="AG101" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -8722,14 +8974,14 @@
         <v>0</v>
       </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-326900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-729000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>16</v>
       </c>
@@ -8742,8 +8994,8 @@
       <c r="S102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
+      <c r="T102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U102" s="3">
         <v>0</v>
@@ -8763,8 +9015,8 @@
       <c r="Z102" s="3">
         <v>0</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>16</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>16</v>
@@ -8782,6 +9034,9 @@
         <v>16</v>
       </c>
       <c r="AG102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH102" s="3" t="s">
         <v>16</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CAN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="92">
   <si>
     <t>CAN</t>
   </si>
@@ -656,453 +656,465 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>196300</v>
+      </c>
+      <c r="E8" s="3">
         <v>150500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>100200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>88800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>73600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>49100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>33300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>49100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>33300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>47400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>978200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3008800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>201800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2184600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>187300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>153800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>56100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>24000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>26200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>10700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>71300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>103300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>37700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>7200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>40300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>69800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>126000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>153300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>76600</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>181700</v>
+      </c>
+      <c r="E9" s="3">
         <v>133900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>90900</v>
-      </c>
-      <c r="F9" s="3">
-        <v>95100</v>
       </c>
       <c r="G9" s="3">
         <v>95100</v>
       </c>
       <c r="H9" s="3">
+        <v>95100</v>
+      </c>
+      <c r="I9" s="3">
         <v>91000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>102400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>103100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>102400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>143900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>102800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>939900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>744000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1264100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>78300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>696800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>81900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>92900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>29000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>19900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>175000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>80700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>36000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>7100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>38600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>62700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>174600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>40600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>41600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E10" s="3">
         <v>16600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>9300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-6400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-21500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-19100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-54100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-69100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-54100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-69100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-70100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-47500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-892500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>234200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1744700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>123500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1487800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>105400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>60800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>27000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>6400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-103700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>22500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>7100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-48500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>112800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>35000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1138,109 +1150,113 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E12" s="3">
         <v>16300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>16400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>16600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>14800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>14600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>10800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>17200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>10800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>17200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>17900</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>19100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>32800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>118100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>205100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>15200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>117900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>13200</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>9900</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>8100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5600</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>4700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>3800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>6500</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>9600</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>5700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>5600</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>4800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>7400</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>9800</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>5500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>4700</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,64 +1356,67 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E14" s="3">
         <v>1200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-900</v>
       </c>
-      <c r="F14" s="3">
-        <v>18900</v>
-      </c>
       <c r="G14" s="3">
+        <v>25600</v>
+      </c>
+      <c r="H14" s="3">
         <v>33900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-5200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>65500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>5700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>65500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>5700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P14" s="3">
         <v>67200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>30400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>16</v>
+      <c r="T14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>16</v>
@@ -1405,8 +1424,8 @@
       <c r="W14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1441,47 +1460,50 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E15" s="3">
         <v>7100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>14900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>6500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>14900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>14900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8200</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1494,8 +1516,8 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>16</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>16</v>
@@ -1515,15 +1537,15 @@
       <c r="Z15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB15" s="3">
         <v>500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>400</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AD15" s="3" t="s">
         <v>16</v>
       </c>
@@ -1533,8 +1555,8 @@
       <c r="AF15" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1542,8 +1564,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1576,210 +1601,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>211100</v>
+      </c>
+      <c r="E17" s="3">
         <v>173200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>128100</v>
       </c>
-      <c r="F17" s="3">
-        <v>147600</v>
-      </c>
       <c r="G17" s="3">
+        <v>140800</v>
+      </c>
+      <c r="H17" s="3">
         <v>124800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>123600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>136000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>140500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>183800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>140900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>183600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1030300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1816100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>116300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>971300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>121400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>130200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>58000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>15200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>29000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>21800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>194700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>91900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>79600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>51200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>79700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>188800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>51000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>58400</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-27900</v>
       </c>
-      <c r="F18" s="3">
-        <v>-58800</v>
-      </c>
       <c r="G18" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-51200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-51800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-86900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-107200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-86900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-107200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-110000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-85700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-136200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-52100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1192700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>85500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1213300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>65900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>23500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-9900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-13700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-11100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-123400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-42000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-9900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-62800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>102400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>18200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1815,148 +1847,152 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E20" s="3">
         <v>3000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-70200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>9900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-12200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>9900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-12200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>110200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>147200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>123400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>7000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>9800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-18600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-1300</v>
       </c>
-      <c r="F21" s="3">
-        <v>18500</v>
-      </c>
       <c r="G21" s="3">
+        <v>25300</v>
+      </c>
+      <c r="H21" s="3">
         <v>-33300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-42500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-81900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-86500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-81900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-86500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-89600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-78900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>16</v>
       </c>
@@ -1993,52 +2029,55 @@
       <c r="AA21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC21" s="3">
         <v>16500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-39400</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE21" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG21" s="3">
         <v>-7000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-52400</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AI21" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ21" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="E22" s="3">
         <v>400</v>
       </c>
       <c r="F22" s="3">
+        <v>400</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>200</v>
       </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>16</v>
+      <c r="I22" s="3">
+        <v>0</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>16</v>
@@ -2055,23 +2094,23 @@
       <c r="N22" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -2083,10 +2122,10 @@
         <v>0</v>
       </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>100</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>200</v>
       </c>
       <c r="Z22" s="3">
         <v>200</v>
@@ -2095,186 +2134,192 @@
         <v>200</v>
       </c>
       <c r="AB22" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC22" s="3">
         <v>300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>2000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>2700</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>2400</v>
       </c>
       <c r="AG22" s="3">
         <v>2400</v>
       </c>
       <c r="AH22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AI22" s="3">
         <v>100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-84200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-27200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-82300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-43800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-162100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-100500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-162100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-100500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-116100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-86700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-123500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>58000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1339800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>86000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1336600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>72800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-12100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-55400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>106600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>21400</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>85300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-6700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-23100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-20400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-23100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-20400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-27200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>304400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>20900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>49800</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -2306,22 +2351,25 @@
         <v>0</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>13300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2421,210 +2469,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-27700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-11100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-92900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-75600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-139000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-80100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-139000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-80100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-110700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-84400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-96300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>61100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1035500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>65100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1286900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>72800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-10000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>14600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>93300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-27700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-11100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-92900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-75600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-139000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-80100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-139000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-80100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-110700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-84400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-96300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>61100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1035500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>65100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1286900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>72800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-10000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>14600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>93300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2781,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2825,8 +2885,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2926,8 +2989,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3027,210 +3093,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>70200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-9900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>12200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-9900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>12200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-110200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-147200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-123400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-7000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-9800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-27700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-11100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-92900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-75600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-139000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-80100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-139000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-80100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-110700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-84400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-96300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>61100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1035500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>65100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1286900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>72800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-10000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>14600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>93300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3330,215 +3405,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-27700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-11100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-92900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-75600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-139000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-80100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-139000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-80100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-110700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-84400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-96300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>61100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1035500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>65100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1286900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>72800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-10000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>14600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>93300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3574,8 +3658,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3611,92 +3696,93 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E41" s="3">
         <v>119200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>65900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>96500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>66800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>96200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>40600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>96200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>40600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>101600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2002700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2640700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2643200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2684300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>241400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>173500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>186200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>54500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>26100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>23100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>41400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>80400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>51200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>42200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE41" s="3" t="s">
         <v>16</v>
       </c>
@@ -3712,38 +3798,41 @@
       <c r="AI41" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ41" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>1900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2200</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>3300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>3700</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3772,32 +3861,32 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>1200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>30100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>51200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>27100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>1700</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>12500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>17200</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>16</v>
       </c>
@@ -3813,92 +3902,95 @@
       <c r="AI42" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ42" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>129800</v>
+      </c>
+      <c r="E43" s="3">
         <v>120200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>59700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>58400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>58400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>10100</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="O43" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P43" s="3">
         <v>504300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>357900</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>275000</v>
-      </c>
-      <c r="T43" s="3">
-        <v>100</v>
       </c>
       <c r="U43" s="3">
         <v>100</v>
       </c>
       <c r="V43" s="3">
+        <v>100</v>
+      </c>
+      <c r="W43" s="3">
         <v>1000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>14000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>24800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>23700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>26400</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE43" s="3" t="s">
         <v>16</v>
       </c>
@@ -3914,92 +4006,95 @@
       <c r="AI43" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ43" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E44" s="3">
         <v>201700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>108000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>94600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>87800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>131300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>142300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>217100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>142300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>217100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>272100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>310500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1685600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1328900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1626200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1193300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>812400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>118400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>83500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>52400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>31400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>13000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>35500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>30200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>60400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>65500</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE44" s="3" t="s">
         <v>16</v>
       </c>
@@ -4015,92 +4110,95 @@
       <c r="AI44" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ44" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="3">
         <v>117300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>26100</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="3">
         <v>74900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63100</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="3">
         <v>63100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P45" s="3">
         <v>1427300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1335300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1420300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1937600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1501800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>186200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>201800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>31700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>37000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>26600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>40800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>74700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>64800</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE45" s="3" t="s">
         <v>16</v>
       </c>
@@ -4116,92 +4214,95 @@
       <c r="AI45" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ45" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>433300</v>
+      </c>
+      <c r="E46" s="3">
         <v>517400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>421000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>334000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>307500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>336000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>363700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>349200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>363700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>349200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>431800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>520800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>555700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5024700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5687200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5774100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5273500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>546200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>458800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>323500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>140200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>101100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>115400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>145900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>144900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>222500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>216100</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE46" s="3" t="s">
         <v>16</v>
       </c>
@@ -4217,8 +4318,11 @@
       <c r="AI46" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ46" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4232,10 +4336,10 @@
         <v>2800</v>
       </c>
       <c r="G47" s="3">
+        <v>2800</v>
+      </c>
+      <c r="H47" s="3">
         <v>2900</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2800</v>
       </c>
       <c r="I47" s="3">
         <v>2800</v>
@@ -4253,13 +4357,13 @@
         <v>2800</v>
       </c>
       <c r="N47" s="3">
-        <v>2900</v>
+        <v>2800</v>
       </c>
       <c r="O47" s="3">
         <v>2900</v>
       </c>
       <c r="P47" s="3">
-        <v>20000</v>
+        <v>2900</v>
       </c>
       <c r="Q47" s="3">
         <v>20000</v>
@@ -4271,11 +4375,11 @@
         <v>20000</v>
       </c>
       <c r="T47" s="3">
+        <v>20000</v>
+      </c>
+      <c r="U47" s="3">
         <v>2800</v>
       </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
@@ -4283,11 +4387,11 @@
         <v>0</v>
       </c>
       <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
         <v>400</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>16</v>
       </c>
@@ -4303,8 +4407,8 @@
       <c r="AD47" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
@@ -4318,92 +4422,95 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46900</v>
+      </c>
+      <c r="E48" s="3">
         <v>63700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>72700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>43700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>43500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>53400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>717200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>355400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>357200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>340600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>216500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>18200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>21200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8200</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE48" s="3" t="s">
         <v>16</v>
       </c>
@@ -4419,8 +4526,11 @@
       <c r="AI48" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ48" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4428,19 +4538,19 @@
         <v>700</v>
       </c>
       <c r="E49" s="3">
+        <v>700</v>
+      </c>
+      <c r="F49" s="3">
         <v>800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>1000</v>
       </c>
       <c r="H49" s="3">
         <v>1000</v>
       </c>
       <c r="I49" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -4458,34 +4568,34 @@
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>12500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>74100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>51300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>45300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>20300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>900</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>16</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -4520,8 +4630,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4621,8 +4734,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4722,67 +4838,70 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E52" s="3">
         <v>85100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>94600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>81400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>70300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>28800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>16100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>107300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>78900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>70600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>102000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
-      </c>
-      <c r="V52" s="3">
-        <v>400</v>
       </c>
       <c r="W52" s="3">
         <v>400</v>
@@ -4791,23 +4910,23 @@
         <v>400</v>
       </c>
       <c r="Y52" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z52" s="3">
         <v>300</v>
       </c>
       <c r="AA52" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB52" s="3">
         <v>800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>1000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE52" s="3" t="s">
         <v>16</v>
       </c>
@@ -4823,8 +4942,11 @@
       <c r="AI52" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ52" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4924,92 +5046,95 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>602900</v>
+      </c>
+      <c r="E54" s="3">
         <v>670000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>592200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>463000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>502100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>525500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>493300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>464100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>493300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>464100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>538400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>633700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>685000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5581400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6194700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6250500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5632300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>558400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>465900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>328700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>144300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>106800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>133900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>152500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>152700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>245800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>225300</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE54" s="3" t="s">
         <v>16</v>
       </c>
@@ -5025,8 +5150,11 @@
       <c r="AI54" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ54" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5062,8 +5190,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5099,92 +5228,93 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E57" s="3">
         <v>33700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>30000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>29900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>19200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>26900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>32700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>97000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>101200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>143400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>6300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>10300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>11500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>9700</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE57" s="3" t="s">
         <v>16</v>
       </c>
@@ -5200,47 +5330,50 @@
       <c r="AI57" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ57" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E58" s="3">
         <v>46400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>25800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>17900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2400</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5260,32 +5393,32 @@
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>4500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>6800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>28900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>29700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>38300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>30800</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE58" s="3" t="s">
         <v>16</v>
       </c>
@@ -5301,92 +5434,95 @@
       <c r="AI58" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ58" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E59" s="3">
         <v>143400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>160000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>123400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>96900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>65200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>101000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>99600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>11900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>395300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>658600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1379100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2093600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1941700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>188600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>176100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>236300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>70500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>9100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>53200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>54400</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE59" s="3" t="s">
         <v>16</v>
       </c>
@@ -5402,92 +5538,95 @@
       <c r="AI59" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ59" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>131100</v>
+      </c>
+      <c r="E60" s="3">
         <v>279000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>236900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>178600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>151200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>116800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>135200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>135200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>83000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>691300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1476100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2194800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2085100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>205700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>191400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>247100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>82500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>24500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>36300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>45700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>43900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>103000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>94900</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE60" s="3" t="s">
         <v>16</v>
       </c>
@@ -5503,47 +5642,50 @@
       <c r="AI60" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ60" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>25600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>21000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>700</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -5604,92 +5746,95 @@
       <c r="AI61" s="3">
         <v>0</v>
       </c>
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>400</v>
+      </c>
+      <c r="E62" s="3">
         <v>9700</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="F62" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H62" s="3">
         <v>9400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>18700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>16900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>85100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>88500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>10500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>3300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2900</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE62" s="3" t="s">
         <v>16</v>
       </c>
@@ -5705,8 +5850,11 @@
       <c r="AI62" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ62" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5806,8 +5954,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5907,8 +6058,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6008,92 +6162,95 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>165500</v>
+      </c>
+      <c r="E66" s="3">
         <v>290100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>268600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>196800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>186300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>147300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>145100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>100700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>145100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>100700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>112300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>85600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>710000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1492900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2280000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2173600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>208300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>201900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>248300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>84100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>26700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>38900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>49000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>46000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>105700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>97800</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE66" s="3" t="s">
         <v>16</v>
       </c>
@@ -6109,8 +6266,11 @@
       <c r="AI66" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ66" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6146,8 +6306,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6247,8 +6408,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6348,8 +6512,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6449,8 +6616,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6550,92 +6720,95 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-645900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-560800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-533100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-435600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-342700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-267100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-204700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-65700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-204700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-65700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>125100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>209400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1932800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1886700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1277800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>900800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-65800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-121100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-152700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-152900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-151300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-138500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-144500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-136000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-13100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE72" s="3" t="s">
         <v>16</v>
       </c>
@@ -6651,8 +6824,11 @@
       <c r="AI72" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ72" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6752,8 +6928,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6853,8 +7032,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6954,92 +7136,95 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>437400</v>
+      </c>
+      <c r="E76" s="3">
         <v>379900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>323600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>266300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>315800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>378200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>348200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>363400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>348200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>363400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>426100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>548100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>607700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4871400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4701800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3970600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3458700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>350100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>264000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>80500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>60200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>80100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>95000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>103500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>106700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>140100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>127500</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="AE76" s="3" t="s">
         <v>16</v>
       </c>
@@ -7055,8 +7240,11 @@
       <c r="AI76" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ76" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7156,215 +7344,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-27700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-11100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-92900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-75600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-139000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-80100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-139000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-80100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-110700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-84400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-96300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>61100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1035500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>65100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1286900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>72800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-10000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-12700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-122900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>14600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-41000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-10400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-9700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-62200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>93300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7400,8 +7597,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7420,26 +7618,26 @@
       <c r="H83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J83" s="3">
         <v>14900</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="3">
         <v>14900</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -7480,8 +7678,8 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-      <c r="AC83" s="3" t="s">
-        <v>16</v>
+      <c r="AC83" s="3">
+        <v>0</v>
       </c>
       <c r="AD83" s="3" t="s">
         <v>16</v>
@@ -7501,8 +7699,11 @@
       <c r="AI83" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ83" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7602,8 +7803,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7703,8 +7907,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7804,8 +8011,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7905,8 +8115,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8006,8 +8219,11 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8044,15 +8260,15 @@
       <c r="N89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P89" s="3">
         <v>-182600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-582200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>16</v>
       </c>
@@ -8065,8 +8281,8 @@
       <c r="U89" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="V89" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
@@ -8086,8 +8302,8 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-      <c r="AC89" s="3" t="s">
-        <v>16</v>
+      <c r="AC89" s="3">
+        <v>0</v>
       </c>
       <c r="AD89" s="3" t="s">
         <v>16</v>
@@ -8107,8 +8323,11 @@
       <c r="AI89" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ89" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8144,8 +8363,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8182,8 +8402,8 @@
       <c r="N91" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -8224,8 +8444,8 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>16</v>
+      <c r="AC91" s="3">
+        <v>0</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>16</v>
@@ -8245,8 +8465,11 @@
       <c r="AI91" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ91" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8346,8 +8569,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8447,8 +8673,11 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -8485,15 +8714,15 @@
       <c r="N94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P94" s="3">
         <v>-8100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-40300</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>16</v>
       </c>
@@ -8506,8 +8735,8 @@
       <c r="U94" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
@@ -8527,8 +8756,8 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-      <c r="AC94" s="3" t="s">
-        <v>16</v>
+      <c r="AC94" s="3">
+        <v>0</v>
       </c>
       <c r="AD94" s="3" t="s">
         <v>16</v>
@@ -8548,8 +8777,11 @@
       <c r="AI94" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ94" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8585,8 +8817,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8623,8 +8856,8 @@
       <c r="N96" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -8686,8 +8919,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8787,8 +9023,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8888,8 +9127,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8989,8 +9231,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9027,15 +9272,15 @@
       <c r="N100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P100" s="3">
         <v>-56200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-315600</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>16</v>
       </c>
@@ -9048,8 +9293,8 @@
       <c r="U100" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="V100" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
@@ -9069,8 +9314,8 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-      <c r="AC100" s="3" t="s">
-        <v>16</v>
+      <c r="AC100" s="3">
+        <v>0</v>
       </c>
       <c r="AD100" s="3" t="s">
         <v>16</v>
@@ -9090,8 +9335,11 @@
       <c r="AI100" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ100" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9110,33 +9358,33 @@
       <c r="H101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J101" s="3">
         <v>-110300</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L101" s="3">
         <v>-110300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P101" s="3">
         <v>-80000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>209000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>16</v>
       </c>
@@ -9149,8 +9397,8 @@
       <c r="U101" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
+      <c r="V101" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W101" s="3">
         <v>0</v>
@@ -9170,8 +9418,8 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-      <c r="AC101" s="3" t="s">
-        <v>16</v>
+      <c r="AC101" s="3">
+        <v>0</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>16</v>
@@ -9191,8 +9439,11 @@
       <c r="AI101" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="AJ101" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9230,14 +9481,14 @@
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>-326900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-729000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>16</v>
       </c>
@@ -9250,8 +9501,8 @@
       <c r="U102" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="V102" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
@@ -9271,8 +9522,8 @@
       <c r="AB102" s="3">
         <v>0</v>
       </c>
-      <c r="AC102" s="3" t="s">
-        <v>16</v>
+      <c r="AC102" s="3">
+        <v>0</v>
       </c>
       <c r="AD102" s="3" t="s">
         <v>16</v>
@@ -9290,6 +9541,9 @@
         <v>16</v>
       </c>
       <c r="AI102" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ102" s="3" t="s">
         <v>16</v>
       </c>
     </row>
